--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F01A2-4491-4E9B-92FF-4AF067A28093}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2C5719-FD2D-40A2-A2EB-52434DFD12C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -273,14 +273,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -16043,7 +16043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S167"/>
+  <dimension ref="A1:S169"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -16056,16 +16056,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -16112,10 +16112,10 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="9"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="10"/>
       <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
@@ -25561,6 +25561,118 @@
       </c>
       <c r="R167" s="7">
         <v>886</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A168" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B168" s="3">
+        <v>46084</v>
+      </c>
+      <c r="C168" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E168" s="7">
+        <v>1614</v>
+      </c>
+      <c r="F168" s="7">
+        <v>1974</v>
+      </c>
+      <c r="G168" s="7">
+        <v>2826</v>
+      </c>
+      <c r="H168" s="7">
+        <v>2291</v>
+      </c>
+      <c r="I168" s="7">
+        <v>3188</v>
+      </c>
+      <c r="J168" s="7">
+        <v>2062</v>
+      </c>
+      <c r="K168" s="7">
+        <v>1662</v>
+      </c>
+      <c r="L168" s="7">
+        <v>1769</v>
+      </c>
+      <c r="M168" s="7">
+        <v>2181</v>
+      </c>
+      <c r="N168" s="7">
+        <v>2703</v>
+      </c>
+      <c r="O168" s="7">
+        <v>3119</v>
+      </c>
+      <c r="P168" s="7">
+        <v>51</v>
+      </c>
+      <c r="Q168" s="7">
+        <v>220</v>
+      </c>
+      <c r="R168" s="7">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A169" s="3">
+        <v>46090</v>
+      </c>
+      <c r="B169" s="3">
+        <v>46090</v>
+      </c>
+      <c r="C169" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E169" s="7">
+        <v>1767</v>
+      </c>
+      <c r="F169" s="7">
+        <v>2036</v>
+      </c>
+      <c r="G169" s="7">
+        <v>2962</v>
+      </c>
+      <c r="H169" s="7">
+        <v>2315</v>
+      </c>
+      <c r="I169" s="7">
+        <v>3221</v>
+      </c>
+      <c r="J169" s="7">
+        <v>3622</v>
+      </c>
+      <c r="K169" s="7">
+        <v>1579</v>
+      </c>
+      <c r="L169" s="7">
+        <v>2377</v>
+      </c>
+      <c r="M169" s="7">
+        <v>2634</v>
+      </c>
+      <c r="N169" s="7">
+        <v>2675</v>
+      </c>
+      <c r="O169" s="7">
+        <v>3210</v>
+      </c>
+      <c r="P169" s="7">
+        <v>51</v>
+      </c>
+      <c r="Q169" s="7">
+        <v>220</v>
+      </c>
+      <c r="R169" s="7">
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -25593,7 +25705,7 @@
       <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>37</v>
       </c>
     </row>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2C5719-FD2D-40A2-A2EB-52434DFD12C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D185B2B0-6795-4634-B93D-78F3087C9984}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -16043,7 +16043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S169"/>
+  <dimension ref="A1:S170"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -25673,6 +25673,62 @@
       </c>
       <c r="R169" s="7">
         <v>865</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A170" s="3">
+        <v>46097</v>
+      </c>
+      <c r="B170" s="3">
+        <v>46097</v>
+      </c>
+      <c r="C170" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E170" s="7">
+        <v>1879</v>
+      </c>
+      <c r="F170" s="7">
+        <v>2046</v>
+      </c>
+      <c r="G170" s="7">
+        <v>3013</v>
+      </c>
+      <c r="H170" s="7">
+        <v>2461</v>
+      </c>
+      <c r="I170" s="7">
+        <v>3573</v>
+      </c>
+      <c r="J170" s="7">
+        <v>4401</v>
+      </c>
+      <c r="K170" s="7">
+        <v>1492</v>
+      </c>
+      <c r="L170" s="7">
+        <v>2701</v>
+      </c>
+      <c r="M170" s="7">
+        <v>2765</v>
+      </c>
+      <c r="N170" s="7">
+        <v>2796</v>
+      </c>
+      <c r="O170" s="7">
+        <v>3517</v>
+      </c>
+      <c r="P170" s="7">
+        <v>52</v>
+      </c>
+      <c r="Q170" s="7">
+        <v>220</v>
+      </c>
+      <c r="R170" s="7">
+        <v>902</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D185B2B0-6795-4634-B93D-78F3087C9984}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A3131B-F127-4ACB-8922-F8FA22BD5DE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -16043,7 +16043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S170"/>
+  <dimension ref="A1:S171"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -25729,6 +25729,62 @@
       </c>
       <c r="R170" s="7">
         <v>902</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A171" s="3">
+        <v>46084</v>
+      </c>
+      <c r="B171" s="3">
+        <v>46084</v>
+      </c>
+      <c r="C171" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E171" s="7">
+        <v>2027</v>
+      </c>
+      <c r="F171" s="7">
+        <v>2299</v>
+      </c>
+      <c r="G171" s="7">
+        <v>3184</v>
+      </c>
+      <c r="H171" s="7">
+        <v>2600</v>
+      </c>
+      <c r="I171" s="7">
+        <v>3807</v>
+      </c>
+      <c r="J171" s="7">
+        <v>4876</v>
+      </c>
+      <c r="K171" s="7">
+        <v>1570</v>
+      </c>
+      <c r="L171" s="7">
+        <v>2988</v>
+      </c>
+      <c r="M171" s="7">
+        <v>2856</v>
+      </c>
+      <c r="N171" s="7">
+        <v>3004</v>
+      </c>
+      <c r="O171" s="7">
+        <v>3721</v>
+      </c>
+      <c r="P171" s="7">
+        <v>55</v>
+      </c>
+      <c r="Q171" s="7">
+        <v>230</v>
+      </c>
+      <c r="R171" s="7">
+        <v>998</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A3131B-F127-4ACB-8922-F8FA22BD5DE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F14890-6CEC-46DA-8353-D1F6D18EF0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="KCCI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -170,11 +170,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -238,14 +239,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -258,16 +259,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -279,14 +280,20 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -304,7 +311,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -352,10 +359,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -847,16 +854,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$E$3:$E$166</c:f>
+              <c:f>KCCI!$E$3:$E$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>2892</c:v>
                 </c:pt>
@@ -1348,6 +1373,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>1597</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1522</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1614</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1767</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>2094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1390,10 +1433,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -1885,16 +1928,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$F$3:$F$166</c:f>
+              <c:f>KCCI!$F$3:$F$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>1934</c:v>
                 </c:pt>
@@ -2386,6 +2447,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1823</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2299</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>2362</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2428,10 +2507,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -2923,16 +3002,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$G$3:$G$166</c:f>
+              <c:f>KCCI!$G$3:$G$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>5383</c:v>
                 </c:pt>
@@ -3424,6 +3521,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>2854</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>2658</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2826</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2962</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3013</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3184</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3196</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3466,10 +3581,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -3961,16 +4076,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$H$3:$H$166</c:f>
+              <c:f>KCCI!$H$3:$H$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>4016</c:v>
                 </c:pt>
@@ -4462,6 +4595,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>2407</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>2253</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2291</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2315</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2461</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>2718</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4504,10 +4655,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -4999,16 +5150,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$I$3:$I$166</c:f>
+              <c:f>KCCI!$I$3:$I$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>4475</c:v>
                 </c:pt>
@@ -5500,6 +5669,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>3483</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3176</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3188</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3221</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3573</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3807</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3896</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5542,10 +5729,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -6037,16 +6224,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$J$3:$J$166</c:f>
+              <c:f>KCCI!$J$3:$J$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>3359</c:v>
                 </c:pt>
@@ -6538,6 +6743,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3622</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4401</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4876</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>5394</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6582,10 +6805,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -7077,16 +7300,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$K$3:$K$166</c:f>
+              <c:f>KCCI!$K$3:$K$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>4166</c:v>
                 </c:pt>
@@ -7578,6 +7819,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1749</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1662</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1579</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1492</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1570</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1518</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7622,10 +7881,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -8117,16 +8376,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$L$3:$L$166</c:f>
+              <c:f>KCCI!$L$3:$L$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>5075</c:v>
                 </c:pt>
@@ -8618,6 +8895,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>1556</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1522</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1769</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2377</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2701</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2988</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3033</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8662,10 +8957,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -9157,16 +9452,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$M$3:$M$166</c:f>
+              <c:f>KCCI!$M$3:$M$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>3854</c:v>
                 </c:pt>
@@ -9658,6 +9971,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>1248</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1561</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2181</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2634</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2765</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2856</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>2884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9702,10 +10033,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -10197,16 +10528,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$N$3:$N$166</c:f>
+              <c:f>KCCI!$N$3:$N$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>6459</c:v>
                 </c:pt>
@@ -10698,6 +11047,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>2760</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>2558</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2703</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2675</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2796</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3004</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3008</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10742,10 +11109,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -11237,16 +11604,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$O$3:$O$166</c:f>
+              <c:f>KCCI!$O$3:$O$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>6028</c:v>
                 </c:pt>
@@ -11738,6 +12123,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>3084</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3055</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3119</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3210</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3517</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3721</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11798,10 +12201,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -12293,16 +12696,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$P$3:$P$166</c:f>
+              <c:f>KCCI!$P$3:$P$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>295</c:v>
                 </c:pt>
@@ -12794,6 +13215,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12839,10 +13278,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -13334,16 +13773,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$Q$3:$Q$166</c:f>
+              <c:f>KCCI!$Q$3:$Q$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>881</c:v>
                 </c:pt>
@@ -13835,6 +14292,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13880,10 +14355,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$166</c:f>
+              <c:f>KCCI!$B$3:$B$11166</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -14375,16 +14850,34 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$R$3:$R$166</c:f>
+              <c:f>KCCI!$R$3:$R$11166</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="164"/>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>1708</c:v>
                 </c:pt>
@@ -14876,6 +15369,24 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>888</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>886</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>876</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>902</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>998</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14975,7 +15486,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -15017,7 +15528,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -15059,7 +15570,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -15110,6 +15621,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15117,7 +15629,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15747,9 +16258,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -15787,7 +16298,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15893,7 +16404,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16035,7 +16546,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -16043,23 +16554,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S171"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S172"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="3" customWidth="1"/>
-    <col min="5" max="18" width="12.85546875" style="7" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="13.1796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" style="3" customWidth="1"/>
+    <col min="5" max="18" width="12.81640625" style="7" customWidth="1"/>
+    <col min="19" max="19" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:19">
+      <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="11" t="s">
@@ -16111,9 +16622,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+    <row r="2" spans="1:19">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
       <c r="C2" s="11"/>
       <c r="D2" s="10"/>
       <c r="E2" s="6" t="s">
@@ -16159,11 +16670,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:19">
+      <c r="A3" s="13">
         <v>44872</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="13">
         <v>44872</v>
       </c>
       <c r="C3" s="4">
@@ -16216,11 +16727,11 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" spans="1:19">
+      <c r="A4" s="13">
         <v>44879</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="13">
         <v>44879</v>
       </c>
       <c r="C4" s="4">
@@ -16273,11 +16784,11 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:19">
+      <c r="A5" s="13">
         <v>44886</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="13">
         <v>44886</v>
       </c>
       <c r="C5" s="4">
@@ -16330,11 +16841,11 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" spans="1:19">
+      <c r="A6" s="13">
         <v>44893</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="13">
         <v>44893</v>
       </c>
       <c r="C6" s="4">
@@ -16387,11 +16898,11 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:19">
+      <c r="A7" s="13">
         <v>44900</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="13">
         <v>44900</v>
       </c>
       <c r="C7" s="4">
@@ -16444,11 +16955,11 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:19">
+      <c r="A8" s="13">
         <v>44907</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="13">
         <v>44907</v>
       </c>
       <c r="C8" s="4">
@@ -16501,11 +17012,11 @@
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:19">
+      <c r="A9" s="13">
         <v>44914</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="13">
         <v>44914</v>
       </c>
       <c r="C9" s="4">
@@ -16558,11 +17069,11 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:19">
+      <c r="A10" s="13">
         <v>44921</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="13">
         <v>44921</v>
       </c>
       <c r="C10" s="4">
@@ -16615,11 +17126,11 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:19">
+      <c r="A11" s="13">
         <v>44928</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="13">
         <v>44928</v>
       </c>
       <c r="C11" s="4">
@@ -16672,11 +17183,11 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:19">
+      <c r="A12" s="13">
         <v>44935</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="13">
         <v>44935</v>
       </c>
       <c r="C12" s="4">
@@ -16729,11 +17240,11 @@
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:19">
+      <c r="A13" s="13">
         <v>44942</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="13">
         <v>44942</v>
       </c>
       <c r="C13" s="4">
@@ -16786,11 +17297,11 @@
       </c>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:19">
+      <c r="A14" s="13">
         <v>44951</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="13">
         <v>44951</v>
       </c>
       <c r="C14" s="4">
@@ -16843,11 +17354,11 @@
       </c>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" spans="1:19">
+      <c r="A15" s="13">
         <v>44956</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="13">
         <v>44956</v>
       </c>
       <c r="C15" s="4">
@@ -16900,11 +17411,11 @@
       </c>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" spans="1:19">
+      <c r="A16" s="13">
         <v>44963</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="13">
         <v>44963</v>
       </c>
       <c r="C16" s="4">
@@ -16957,11 +17468,11 @@
       </c>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:19">
+      <c r="A17" s="13">
         <v>44970</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="13">
         <v>44970</v>
       </c>
       <c r="C17" s="4">
@@ -17014,11 +17525,11 @@
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" spans="1:19">
+      <c r="A18" s="13">
         <v>44977</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="13">
         <v>44977</v>
       </c>
       <c r="C18" s="4">
@@ -17071,11 +17582,11 @@
       </c>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="19" spans="1:19">
+      <c r="A19" s="13">
         <v>44984</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="13">
         <v>44984</v>
       </c>
       <c r="C19" s="4">
@@ -17128,11 +17639,11 @@
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" spans="1:19">
+      <c r="A20" s="13">
         <v>44991</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="13">
         <v>44991</v>
       </c>
       <c r="C20" s="4">
@@ -17185,11 +17696,11 @@
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="21" spans="1:19">
+      <c r="A21" s="13">
         <v>44998</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="13">
         <v>44998</v>
       </c>
       <c r="C21" s="4">
@@ -17242,11 +17753,11 @@
       </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+    <row r="22" spans="1:19">
+      <c r="A22" s="13">
         <v>45005</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="13">
         <v>45005</v>
       </c>
       <c r="C22" s="4">
@@ -17299,11 +17810,11 @@
       </c>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="23" spans="1:19">
+      <c r="A23" s="13">
         <v>45012</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="13">
         <v>45012</v>
       </c>
       <c r="C23" s="4">
@@ -17356,11 +17867,11 @@
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:19">
+      <c r="A24" s="13">
         <v>45019</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="13">
         <v>45019</v>
       </c>
       <c r="C24" s="4">
@@ -17413,11 +17924,11 @@
       </c>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="25" spans="1:19">
+      <c r="A25" s="13">
         <v>45026</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="13">
         <v>45026</v>
       </c>
       <c r="C25" s="4">
@@ -17470,11 +17981,11 @@
       </c>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="26" spans="1:19">
+      <c r="A26" s="13">
         <v>45033</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="13">
         <v>45033</v>
       </c>
       <c r="C26" s="4">
@@ -17527,11 +18038,11 @@
       </c>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" spans="1:19">
+      <c r="A27" s="13">
         <v>45040</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="13">
         <v>45040</v>
       </c>
       <c r="C27" s="4">
@@ -17584,11 +18095,11 @@
       </c>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+    <row r="28" spans="1:19">
+      <c r="A28" s="13">
         <v>45048</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="13">
         <v>45048</v>
       </c>
       <c r="C28" s="4">
@@ -17641,11 +18152,11 @@
       </c>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" spans="1:19">
+      <c r="A29" s="13">
         <v>45054</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="13">
         <v>45054</v>
       </c>
       <c r="C29" s="4">
@@ -17698,11 +18209,11 @@
       </c>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="30" spans="1:19">
+      <c r="A30" s="13">
         <v>45061</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="13">
         <v>45061</v>
       </c>
       <c r="C30" s="4">
@@ -17755,11 +18266,11 @@
       </c>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="31" spans="1:19">
+      <c r="A31" s="13">
         <v>45068</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="13">
         <v>45068</v>
       </c>
       <c r="C31" s="4">
@@ -17812,11 +18323,11 @@
       </c>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+    <row r="32" spans="1:19">
+      <c r="A32" s="13">
         <v>45076</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="13">
         <v>45076</v>
       </c>
       <c r="C32" s="4">
@@ -17869,11 +18380,11 @@
       </c>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+    <row r="33" spans="1:19">
+      <c r="A33" s="13">
         <v>45082</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="13">
         <v>45082</v>
       </c>
       <c r="C33" s="4">
@@ -17926,11 +18437,11 @@
       </c>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" spans="1:19">
+      <c r="A34" s="13">
         <v>45089</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="13">
         <v>45089</v>
       </c>
       <c r="C34" s="4">
@@ -17983,11 +18494,11 @@
       </c>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" spans="1:19">
+      <c r="A35" s="13">
         <v>45096</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="13">
         <v>45096</v>
       </c>
       <c r="C35" s="4">
@@ -18040,11 +18551,11 @@
       </c>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="36" spans="1:19">
+      <c r="A36" s="13">
         <v>45103</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="13">
         <v>45103</v>
       </c>
       <c r="C36" s="4">
@@ -18097,11 +18608,11 @@
       </c>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="37" spans="1:19">
+      <c r="A37" s="13">
         <v>45110</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="13">
         <v>45110</v>
       </c>
       <c r="C37" s="4">
@@ -18154,11 +18665,11 @@
       </c>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="38" spans="1:19">
+      <c r="A38" s="13">
         <v>45117</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="13">
         <v>45117</v>
       </c>
       <c r="C38" s="4">
@@ -18211,11 +18722,11 @@
       </c>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="39" spans="1:19">
+      <c r="A39" s="13">
         <v>45124</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="13">
         <v>45124</v>
       </c>
       <c r="C39" s="4">
@@ -18268,11 +18779,11 @@
       </c>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+    <row r="40" spans="1:19">
+      <c r="A40" s="13">
         <v>45131</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="13">
         <v>45131</v>
       </c>
       <c r="C40" s="4">
@@ -18325,11 +18836,11 @@
       </c>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+    <row r="41" spans="1:19">
+      <c r="A41" s="13">
         <v>45138</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="13">
         <v>45138</v>
       </c>
       <c r="C41" s="4">
@@ -18382,11 +18893,11 @@
       </c>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="42" spans="1:19">
+      <c r="A42" s="13">
         <v>45145</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="13">
         <v>45145</v>
       </c>
       <c r="C42" s="4">
@@ -18439,11 +18950,11 @@
       </c>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="43" spans="1:19">
+      <c r="A43" s="13">
         <v>45152</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="13">
         <v>45152</v>
       </c>
       <c r="C43" s="4">
@@ -18496,11 +19007,11 @@
       </c>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="44" spans="1:19">
+      <c r="A44" s="13">
         <v>45159</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="13">
         <v>45159</v>
       </c>
       <c r="C44" s="4">
@@ -18553,11 +19064,11 @@
       </c>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="45" spans="1:19">
+      <c r="A45" s="13">
         <v>45166</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="13">
         <v>45166</v>
       </c>
       <c r="C45" s="4">
@@ -18610,11 +19121,11 @@
       </c>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="46" spans="1:19">
+      <c r="A46" s="13">
         <v>45173</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="13">
         <v>45173</v>
       </c>
       <c r="C46" s="4">
@@ -18667,11 +19178,11 @@
       </c>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="47" spans="1:19">
+      <c r="A47" s="13">
         <v>45180</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="13">
         <v>45180</v>
       </c>
       <c r="C47" s="4">
@@ -18724,11 +19235,11 @@
       </c>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="48" spans="1:19">
+      <c r="A48" s="13">
         <v>45187</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="13">
         <v>45187</v>
       </c>
       <c r="C48" s="4">
@@ -18781,11 +19292,11 @@
       </c>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" spans="1:19">
+      <c r="A49" s="13">
         <v>45194</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="13">
         <v>45194</v>
       </c>
       <c r="C49" s="4">
@@ -18838,11 +19349,11 @@
       </c>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="50" spans="1:19">
+      <c r="A50" s="13">
         <v>45209</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="13">
         <v>45209</v>
       </c>
       <c r="C50" s="4">
@@ -18895,11 +19406,11 @@
       </c>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+    <row r="51" spans="1:19">
+      <c r="A51" s="13">
         <v>45215</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="13">
         <v>45215</v>
       </c>
       <c r="C51" s="4">
@@ -18952,11 +19463,11 @@
       </c>
       <c r="S51" s="1"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="52" spans="1:19">
+      <c r="A52" s="13">
         <v>45222</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="13">
         <v>45222</v>
       </c>
       <c r="C52" s="4">
@@ -19009,11 +19520,11 @@
       </c>
       <c r="S52" s="1"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="53" spans="1:19">
+      <c r="A53" s="13">
         <v>45229</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="13">
         <v>45229</v>
       </c>
       <c r="C53" s="4">
@@ -19066,11 +19577,11 @@
       </c>
       <c r="S53" s="1"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="54" spans="1:19">
+      <c r="A54" s="13">
         <v>45236</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="13">
         <v>45236</v>
       </c>
       <c r="C54" s="4">
@@ -19123,11 +19634,11 @@
       </c>
       <c r="S54" s="1"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="55" spans="1:19">
+      <c r="A55" s="13">
         <v>45243</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="13">
         <v>45243</v>
       </c>
       <c r="C55" s="4">
@@ -19180,11 +19691,11 @@
       </c>
       <c r="S55" s="1"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+    <row r="56" spans="1:19">
+      <c r="A56" s="13">
         <v>45250</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="13">
         <v>45250</v>
       </c>
       <c r="C56" s="4">
@@ -19237,11 +19748,11 @@
       </c>
       <c r="S56" s="1"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="57" spans="1:19">
+      <c r="A57" s="13">
         <v>45257</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="13">
         <v>45257</v>
       </c>
       <c r="C57" s="4">
@@ -19294,11 +19805,11 @@
       </c>
       <c r="S57" s="1"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+    <row r="58" spans="1:19">
+      <c r="A58" s="13">
         <v>45264</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="13">
         <v>45264</v>
       </c>
       <c r="C58" s="4">
@@ -19351,11 +19862,11 @@
       </c>
       <c r="S58" s="1"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+    <row r="59" spans="1:19">
+      <c r="A59" s="13">
         <v>45271</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="13">
         <v>45271</v>
       </c>
       <c r="C59" s="4">
@@ -19408,11 +19919,11 @@
       </c>
       <c r="S59" s="1"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="60" spans="1:19">
+      <c r="A60" s="13">
         <v>45278</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="13">
         <v>45278</v>
       </c>
       <c r="C60" s="4">
@@ -19465,11 +19976,11 @@
       </c>
       <c r="S60" s="1"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="61" spans="1:19">
+      <c r="A61" s="13">
         <v>45286</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="13">
         <v>45286</v>
       </c>
       <c r="C61" s="4">
@@ -19522,11 +20033,11 @@
       </c>
       <c r="S61" s="1"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+    <row r="62" spans="1:19">
+      <c r="A62" s="13">
         <v>45293</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="13">
         <v>45293</v>
       </c>
       <c r="C62" s="4">
@@ -19579,11 +20090,11 @@
       </c>
       <c r="S62" s="1"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="63" spans="1:19">
+      <c r="A63" s="13">
         <v>45299</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="13">
         <v>45299</v>
       </c>
       <c r="C63" s="4">
@@ -19636,11 +20147,11 @@
       </c>
       <c r="S63" s="1"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="64" spans="1:19">
+      <c r="A64" s="13">
         <v>45306</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="13">
         <v>45306</v>
       </c>
       <c r="C64" s="4">
@@ -19693,11 +20204,11 @@
       </c>
       <c r="S64" s="1"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+    <row r="65" spans="1:19">
+      <c r="A65" s="13">
         <v>45313</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="13">
         <v>45313</v>
       </c>
       <c r="C65" s="4">
@@ -19750,11 +20261,11 @@
       </c>
       <c r="S65" s="1"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="66" spans="1:19">
+      <c r="A66" s="13">
         <v>45320</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="13">
         <v>45320</v>
       </c>
       <c r="C66" s="4">
@@ -19807,11 +20318,11 @@
       </c>
       <c r="S66" s="1"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="67" spans="1:19">
+      <c r="A67" s="13">
         <v>45327</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="13">
         <v>45327</v>
       </c>
       <c r="C67" s="4">
@@ -19864,11 +20375,11 @@
       </c>
       <c r="S67" s="1"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+    <row r="68" spans="1:19">
+      <c r="A68" s="13">
         <v>45335</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="13">
         <v>45335</v>
       </c>
       <c r="C68" s="4">
@@ -19921,11 +20432,11 @@
       </c>
       <c r="S68" s="1"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="69" spans="1:19">
+      <c r="A69" s="13">
         <v>45341</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="13">
         <v>45341</v>
       </c>
       <c r="C69" s="4">
@@ -19978,11 +20489,11 @@
       </c>
       <c r="S69" s="1"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="70" spans="1:19">
+      <c r="A70" s="13">
         <v>45348</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="13">
         <v>45348</v>
       </c>
       <c r="C70" s="4">
@@ -20035,11 +20546,11 @@
       </c>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+    <row r="71" spans="1:19">
+      <c r="A71" s="13">
         <v>45355</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="13">
         <v>45355</v>
       </c>
       <c r="C71" s="4">
@@ -20092,11 +20603,11 @@
       </c>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="72" spans="1:19">
+      <c r="A72" s="13">
         <v>45362</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="13">
         <v>45362</v>
       </c>
       <c r="C72" s="4">
@@ -20149,11 +20660,11 @@
       </c>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+    <row r="73" spans="1:19">
+      <c r="A73" s="13">
         <v>45369</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="13">
         <v>45369</v>
       </c>
       <c r="C73" s="4">
@@ -20206,11 +20717,11 @@
       </c>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+    <row r="74" spans="1:19">
+      <c r="A74" s="13">
         <v>45376</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="13">
         <v>45376</v>
       </c>
       <c r="C74" s="4">
@@ -20263,11 +20774,11 @@
       </c>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+    <row r="75" spans="1:19">
+      <c r="A75" s="13">
         <v>45383</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="13">
         <v>45383</v>
       </c>
       <c r="C75" s="4">
@@ -20320,11 +20831,11 @@
       </c>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+    <row r="76" spans="1:19">
+      <c r="A76" s="13">
         <v>45390</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="13">
         <v>45390</v>
       </c>
       <c r="C76" s="4">
@@ -20377,11 +20888,11 @@
       </c>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+    <row r="77" spans="1:19">
+      <c r="A77" s="13">
         <v>45397</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="13">
         <v>45397</v>
       </c>
       <c r="C77" s="4">
@@ -20434,11 +20945,11 @@
       </c>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+    <row r="78" spans="1:19">
+      <c r="A78" s="13">
         <v>45404</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="13">
         <v>45404</v>
       </c>
       <c r="C78" s="4">
@@ -20491,11 +21002,11 @@
       </c>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
+    <row r="79" spans="1:19">
+      <c r="A79" s="13">
         <v>45411</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="13">
         <v>45411</v>
       </c>
       <c r="C79" s="4">
@@ -20548,11 +21059,11 @@
       </c>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
+    <row r="80" spans="1:19">
+      <c r="A80" s="13">
         <v>45419</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="13">
         <v>45419</v>
       </c>
       <c r="C80" s="4">
@@ -20605,11 +21116,11 @@
       </c>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+    <row r="81" spans="1:19">
+      <c r="A81" s="13">
         <v>45425</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81" s="13">
         <v>45425</v>
       </c>
       <c r="C81" s="4">
@@ -20662,11 +21173,11 @@
       </c>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+    <row r="82" spans="1:19">
+      <c r="A82" s="13">
         <v>45432</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="13">
         <v>45432</v>
       </c>
       <c r="C82" s="4">
@@ -20719,11 +21230,11 @@
       </c>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
+    <row r="83" spans="1:19">
+      <c r="A83" s="13">
         <v>45439</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="13">
         <v>45439</v>
       </c>
       <c r="C83" s="4">
@@ -20776,11 +21287,11 @@
       </c>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+    <row r="84" spans="1:19">
+      <c r="A84" s="13">
         <v>45446</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="13">
         <v>45446</v>
       </c>
       <c r="C84" s="4">
@@ -20833,11 +21344,11 @@
       </c>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+    <row r="85" spans="1:19">
+      <c r="A85" s="13">
         <v>45453</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85" s="13">
         <v>45453</v>
       </c>
       <c r="C85" s="4">
@@ -20890,11 +21401,11 @@
       </c>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+    <row r="86" spans="1:19">
+      <c r="A86" s="13">
         <v>45460</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="13">
         <v>45460</v>
       </c>
       <c r="C86" s="4">
@@ -20947,11 +21458,11 @@
       </c>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
+    <row r="87" spans="1:19">
+      <c r="A87" s="13">
         <v>45467</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87" s="13">
         <v>45467</v>
       </c>
       <c r="C87" s="4">
@@ -21004,11 +21515,11 @@
       </c>
       <c r="S87" s="1"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
+    <row r="88" spans="1:19">
+      <c r="A88" s="13">
         <v>45474</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="13">
         <v>45474</v>
       </c>
       <c r="C88" s="4">
@@ -21061,11 +21572,11 @@
       </c>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
+    <row r="89" spans="1:19">
+      <c r="A89" s="13">
         <v>45481</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="13">
         <v>45481</v>
       </c>
       <c r="C89" s="4">
@@ -21118,11 +21629,11 @@
       </c>
       <c r="S89" s="1"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
+    <row r="90" spans="1:19">
+      <c r="A90" s="13">
         <v>45488</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="13">
         <v>45488</v>
       </c>
       <c r="C90" s="4">
@@ -21175,11 +21686,11 @@
       </c>
       <c r="S90" s="1"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
+    <row r="91" spans="1:19">
+      <c r="A91" s="13">
         <v>45495</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91" s="13">
         <v>45495</v>
       </c>
       <c r="C91" s="4">
@@ -21232,11 +21743,11 @@
       </c>
       <c r="S91" s="1"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+    <row r="92" spans="1:19">
+      <c r="A92" s="13">
         <v>45502</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92" s="13">
         <v>45502</v>
       </c>
       <c r="C92" s="4">
@@ -21289,11 +21800,11 @@
       </c>
       <c r="S92" s="1"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+    <row r="93" spans="1:19">
+      <c r="A93" s="13">
         <v>45509</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93" s="13">
         <v>45509</v>
       </c>
       <c r="C93" s="4">
@@ -21346,11 +21857,11 @@
       </c>
       <c r="S93" s="1"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+    <row r="94" spans="1:19">
+      <c r="A94" s="13">
         <v>45516</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="13">
         <v>45516</v>
       </c>
       <c r="C94" s="4">
@@ -21403,11 +21914,11 @@
       </c>
       <c r="S94" s="1"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+    <row r="95" spans="1:19">
+      <c r="A95" s="13">
         <v>45523</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95" s="13">
         <v>45523</v>
       </c>
       <c r="C95" s="4">
@@ -21460,11 +21971,11 @@
       </c>
       <c r="S95" s="1"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
+    <row r="96" spans="1:19">
+      <c r="A96" s="13">
         <v>45530</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B96" s="13">
         <v>45530</v>
       </c>
       <c r="C96" s="4">
@@ -21517,11 +22028,11 @@
       </c>
       <c r="S96" s="1"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
+    <row r="97" spans="1:19">
+      <c r="A97" s="13">
         <v>45537</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97" s="13">
         <v>45537</v>
       </c>
       <c r="C97" s="4">
@@ -21574,11 +22085,11 @@
       </c>
       <c r="S97" s="1"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
+    <row r="98" spans="1:19">
+      <c r="A98" s="13">
         <v>45544</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="13">
         <v>45544</v>
       </c>
       <c r="C98" s="4">
@@ -21631,11 +22142,11 @@
       </c>
       <c r="S98" s="1"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+    <row r="99" spans="1:19">
+      <c r="A99" s="13">
         <v>45558</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="13">
         <v>45558</v>
       </c>
       <c r="C99" s="4">
@@ -21688,11 +22199,11 @@
       </c>
       <c r="S99" s="1"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
+    <row r="100" spans="1:19">
+      <c r="A100" s="13">
         <v>45565</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="13">
         <v>45565</v>
       </c>
       <c r="C100" s="4">
@@ -21745,11 +22256,11 @@
       </c>
       <c r="S100" s="1"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+    <row r="101" spans="1:19">
+      <c r="A101" s="13">
         <v>45572</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101" s="13">
         <v>45572</v>
       </c>
       <c r="C101" s="4">
@@ -21802,11 +22313,11 @@
       </c>
       <c r="S101" s="1"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
+    <row r="102" spans="1:19">
+      <c r="A102" s="13">
         <v>45579</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102" s="13">
         <v>45579</v>
       </c>
       <c r="C102" s="4">
@@ -21859,11 +22370,11 @@
       </c>
       <c r="S102" s="1"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
+    <row r="103" spans="1:19">
+      <c r="A103" s="13">
         <v>45586</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="13">
         <v>45586</v>
       </c>
       <c r="C103" s="4">
@@ -21916,11 +22427,11 @@
       </c>
       <c r="S103" s="1"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
+    <row r="104" spans="1:19">
+      <c r="A104" s="13">
         <v>45593</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104" s="13">
         <v>45593</v>
       </c>
       <c r="C104" s="4">
@@ -21973,11 +22484,11 @@
       </c>
       <c r="S104" s="1"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
+    <row r="105" spans="1:19">
+      <c r="A105" s="13">
         <v>45600</v>
       </c>
-      <c r="B105" s="3">
+      <c r="B105" s="13">
         <v>45600</v>
       </c>
       <c r="C105" s="4">
@@ -22030,11 +22541,11 @@
       </c>
       <c r="S105" s="1"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
+    <row r="106" spans="1:19">
+      <c r="A106" s="13">
         <v>45607</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106" s="13">
         <v>45607</v>
       </c>
       <c r="C106" s="4">
@@ -22087,11 +22598,11 @@
       </c>
       <c r="S106" s="1"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
+    <row r="107" spans="1:19">
+      <c r="A107" s="13">
         <v>45614</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107" s="13">
         <v>45614</v>
       </c>
       <c r="C107" s="4">
@@ -22144,11 +22655,11 @@
       </c>
       <c r="S107" s="1"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+    <row r="108" spans="1:19">
+      <c r="A108" s="13">
         <v>45621</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108" s="13">
         <v>45621</v>
       </c>
       <c r="C108" s="4">
@@ -22201,11 +22712,11 @@
       </c>
       <c r="S108" s="1"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+    <row r="109" spans="1:19">
+      <c r="A109" s="13">
         <v>45628</v>
       </c>
-      <c r="B109" s="3">
+      <c r="B109" s="13">
         <v>45628</v>
       </c>
       <c r="C109" s="4">
@@ -22258,11 +22769,11 @@
       </c>
       <c r="S109" s="1"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+    <row r="110" spans="1:19">
+      <c r="A110" s="13">
         <v>45635</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110" s="13">
         <v>45635</v>
       </c>
       <c r="C110" s="4">
@@ -22315,11 +22826,11 @@
       </c>
       <c r="S110" s="1"/>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+    <row r="111" spans="1:19">
+      <c r="A111" s="13">
         <v>45642</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111" s="13">
         <v>45642</v>
       </c>
       <c r="C111" s="4">
@@ -22372,11 +22883,11 @@
       </c>
       <c r="S111" s="1"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
+    <row r="112" spans="1:19">
+      <c r="A112" s="13">
         <v>45649</v>
       </c>
-      <c r="B112" s="3">
+      <c r="B112" s="13">
         <v>45649</v>
       </c>
       <c r="C112" s="4">
@@ -22429,11 +22940,11 @@
       </c>
       <c r="S112" s="1"/>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
+    <row r="113" spans="1:19">
+      <c r="A113" s="13">
         <v>45656</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="13">
         <v>45656</v>
       </c>
       <c r="C113" s="4">
@@ -22486,11 +22997,11 @@
       </c>
       <c r="S113" s="1"/>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+    <row r="114" spans="1:19">
+      <c r="A114" s="13">
         <v>45663</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="13">
         <v>45663</v>
       </c>
       <c r="C114" s="4">
@@ -22543,11 +23054,11 @@
       </c>
       <c r="S114" s="1"/>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
+    <row r="115" spans="1:19">
+      <c r="A115" s="13">
         <v>45670</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="13">
         <v>45670</v>
       </c>
       <c r="C115" s="4">
@@ -22600,11 +23111,11 @@
       </c>
       <c r="S115" s="1"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
+    <row r="116" spans="1:19">
+      <c r="A116" s="13">
         <v>45677</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="13">
         <v>45677</v>
       </c>
       <c r="C116" s="4">
@@ -22657,11 +23168,11 @@
       </c>
       <c r="S116" s="1"/>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+    <row r="117" spans="1:19">
+      <c r="A117" s="13">
         <v>45691</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="13">
         <v>45691</v>
       </c>
       <c r="C117" s="4">
@@ -22714,11 +23225,11 @@
       </c>
       <c r="S117" s="1"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+    <row r="118" spans="1:19">
+      <c r="A118" s="13">
         <v>45698</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="13">
         <v>45698</v>
       </c>
       <c r="C118" s="4">
@@ -22771,11 +23282,11 @@
       </c>
       <c r="S118" s="1"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+    <row r="119" spans="1:19">
+      <c r="A119" s="13">
         <v>45705</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="13">
         <v>45705</v>
       </c>
       <c r="C119" s="4">
@@ -22828,11 +23339,11 @@
       </c>
       <c r="S119" s="1"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
+    <row r="120" spans="1:19">
+      <c r="A120" s="13">
         <v>45712</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="13">
         <v>45712</v>
       </c>
       <c r="C120" s="4">
@@ -22885,11 +23396,11 @@
       </c>
       <c r="S120" s="1"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
+    <row r="121" spans="1:19">
+      <c r="A121" s="13">
         <v>45720</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="13">
         <v>45720</v>
       </c>
       <c r="C121" s="4">
@@ -22942,11 +23453,11 @@
       </c>
       <c r="S121" s="1"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
+    <row r="122" spans="1:19">
+      <c r="A122" s="13">
         <v>45726</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="13">
         <v>45726</v>
       </c>
       <c r="C122" s="4">
@@ -22999,11 +23510,11 @@
       </c>
       <c r="S122" s="1"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
+    <row r="123" spans="1:19">
+      <c r="A123" s="13">
         <v>45733</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="13">
         <v>45733</v>
       </c>
       <c r="C123" s="4">
@@ -23056,11 +23567,11 @@
       </c>
       <c r="S123" s="1"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
+    <row r="124" spans="1:19">
+      <c r="A124" s="13">
         <v>45740</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="13">
         <v>45740</v>
       </c>
       <c r="C124" s="4">
@@ -23113,11 +23624,11 @@
       </c>
       <c r="S124" s="1"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
+    <row r="125" spans="1:19">
+      <c r="A125" s="13">
         <v>45747</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="13">
         <v>45747</v>
       </c>
       <c r="C125" s="4">
@@ -23170,11 +23681,11 @@
       </c>
       <c r="S125" s="1"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
+    <row r="126" spans="1:19">
+      <c r="A126" s="13">
         <v>45754</v>
       </c>
-      <c r="B126" s="3">
+      <c r="B126" s="13">
         <v>45754</v>
       </c>
       <c r="C126" s="4">
@@ -23227,11 +23738,11 @@
       </c>
       <c r="S126" s="1"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
+    <row r="127" spans="1:19">
+      <c r="A127" s="13">
         <v>45761</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127" s="13">
         <v>45761</v>
       </c>
       <c r="C127" s="4">
@@ -23284,11 +23795,11 @@
       </c>
       <c r="S127" s="1"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A128" s="3">
+    <row r="128" spans="1:19">
+      <c r="A128" s="13">
         <v>45768</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128" s="13">
         <v>45768</v>
       </c>
       <c r="C128" s="4">
@@ -23341,11 +23852,11 @@
       </c>
       <c r="S128" s="1"/>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A129" s="3">
+    <row r="129" spans="1:19">
+      <c r="A129" s="13">
         <v>45775</v>
       </c>
-      <c r="B129" s="3">
+      <c r="B129" s="13">
         <v>45775</v>
       </c>
       <c r="C129" s="4">
@@ -23398,11 +23909,11 @@
       </c>
       <c r="S129" s="1"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A130" s="3">
+    <row r="130" spans="1:19">
+      <c r="A130" s="13">
         <v>45789</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130" s="13">
         <v>45789</v>
       </c>
       <c r="C130" s="4">
@@ -23455,11 +23966,11 @@
       </c>
       <c r="S130" s="1"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
+    <row r="131" spans="1:19">
+      <c r="A131" s="13">
         <v>45796</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" s="13">
         <v>45796</v>
       </c>
       <c r="C131" s="4">
@@ -23512,11 +24023,11 @@
       </c>
       <c r="S131" s="1"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+    <row r="132" spans="1:19">
+      <c r="A132" s="13">
         <v>45803</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="13">
         <v>45803</v>
       </c>
       <c r="C132" s="4">
@@ -23569,11 +24080,11 @@
       </c>
       <c r="S132" s="1"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A133" s="3">
+    <row r="133" spans="1:19">
+      <c r="A133" s="13">
         <v>45810</v>
       </c>
-      <c r="B133" s="3">
+      <c r="B133" s="13">
         <v>45810</v>
       </c>
       <c r="C133" s="4">
@@ -23626,11 +24137,11 @@
       </c>
       <c r="S133" s="1"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A134" s="3">
+    <row r="134" spans="1:19">
+      <c r="A134" s="13">
         <v>45817</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134" s="13">
         <v>45817</v>
       </c>
       <c r="C134" s="4">
@@ -23683,11 +24194,11 @@
       </c>
       <c r="S134" s="1"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A135" s="3">
+    <row r="135" spans="1:19">
+      <c r="A135" s="13">
         <v>45824</v>
       </c>
-      <c r="B135" s="3">
+      <c r="B135" s="13">
         <v>45824</v>
       </c>
       <c r="C135" s="4">
@@ -23740,11 +24251,11 @@
       </c>
       <c r="S135" s="1"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A136" s="3">
+    <row r="136" spans="1:19">
+      <c r="A136" s="13">
         <v>45831</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136" s="13">
         <v>45831</v>
       </c>
       <c r="C136" s="4">
@@ -23797,11 +24308,11 @@
       </c>
       <c r="S136" s="1"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A137" s="3">
+    <row r="137" spans="1:19">
+      <c r="A137" s="13">
         <v>45838</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137" s="13">
         <v>45838</v>
       </c>
       <c r="C137" s="4">
@@ -23854,11 +24365,11 @@
       </c>
       <c r="S137" s="1"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A138" s="3">
+    <row r="138" spans="1:19">
+      <c r="A138" s="13">
         <v>45845</v>
       </c>
-      <c r="B138" s="3">
+      <c r="B138" s="13">
         <v>45845</v>
       </c>
       <c r="C138" s="4">
@@ -23911,11 +24422,11 @@
       </c>
       <c r="S138" s="1"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A139" s="3">
+    <row r="139" spans="1:19">
+      <c r="A139" s="13">
         <v>45852</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" s="13">
         <v>45852</v>
       </c>
       <c r="C139" s="4">
@@ -23968,11 +24479,11 @@
       </c>
       <c r="S139" s="1"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A140" s="3">
+    <row r="140" spans="1:19">
+      <c r="A140" s="13">
         <v>45859</v>
       </c>
-      <c r="B140" s="3">
+      <c r="B140" s="13">
         <v>45859</v>
       </c>
       <c r="C140" s="4">
@@ -24025,11 +24536,11 @@
       </c>
       <c r="S140" s="1"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A141" s="3">
+    <row r="141" spans="1:19">
+      <c r="A141" s="13">
         <v>45866</v>
       </c>
-      <c r="B141" s="3">
+      <c r="B141" s="13">
         <v>45866</v>
       </c>
       <c r="C141" s="4">
@@ -24082,11 +24593,11 @@
       </c>
       <c r="S141" s="1"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A142" s="3">
+    <row r="142" spans="1:19">
+      <c r="A142" s="13">
         <v>45873</v>
       </c>
-      <c r="B142" s="3">
+      <c r="B142" s="13">
         <v>45873</v>
       </c>
       <c r="C142" s="4">
@@ -24139,11 +24650,11 @@
       </c>
       <c r="S142" s="1"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A143" s="3">
+    <row r="143" spans="1:19">
+      <c r="A143" s="13">
         <v>45880</v>
       </c>
-      <c r="B143" s="3">
+      <c r="B143" s="13">
         <v>45880</v>
       </c>
       <c r="C143" s="4">
@@ -24196,11 +24707,11 @@
       </c>
       <c r="S143" s="1"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A144" s="3">
+    <row r="144" spans="1:19">
+      <c r="A144" s="13">
         <v>45887</v>
       </c>
-      <c r="B144" s="3">
+      <c r="B144" s="13">
         <v>45887</v>
       </c>
       <c r="C144" s="4">
@@ -24253,11 +24764,11 @@
       </c>
       <c r="S144" s="1"/>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A145" s="3">
+    <row r="145" spans="1:19">
+      <c r="A145" s="13">
         <v>45894</v>
       </c>
-      <c r="B145" s="3">
+      <c r="B145" s="13">
         <v>45894</v>
       </c>
       <c r="C145" s="4">
@@ -24310,11 +24821,11 @@
       </c>
       <c r="S145" s="1"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A146" s="3">
+    <row r="146" spans="1:19">
+      <c r="A146" s="13">
         <v>45901</v>
       </c>
-      <c r="B146" s="3">
+      <c r="B146" s="13">
         <v>45901</v>
       </c>
       <c r="C146" s="4">
@@ -24367,11 +24878,11 @@
       </c>
       <c r="S146" s="1"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A147" s="3">
+    <row r="147" spans="1:19">
+      <c r="A147" s="13">
         <v>45908</v>
       </c>
-      <c r="B147" s="3">
+      <c r="B147" s="13">
         <v>45908</v>
       </c>
       <c r="C147" s="4">
@@ -24424,11 +24935,11 @@
       </c>
       <c r="S147" s="1"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A148" s="3">
+    <row r="148" spans="1:19">
+      <c r="A148" s="13">
         <v>45915</v>
       </c>
-      <c r="B148" s="3">
+      <c r="B148" s="13">
         <v>45915</v>
       </c>
       <c r="C148" s="4">
@@ -24481,11 +24992,11 @@
       </c>
       <c r="S148" s="1"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A149" s="3">
+    <row r="149" spans="1:19">
+      <c r="A149" s="13">
         <v>45922</v>
       </c>
-      <c r="B149" s="3">
+      <c r="B149" s="13">
         <v>45922</v>
       </c>
       <c r="C149" s="4">
@@ -24538,11 +25049,11 @@
       </c>
       <c r="S149" s="1"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A150" s="3">
+    <row r="150" spans="1:19">
+      <c r="A150" s="13">
         <v>45929</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B150" s="13">
         <v>45929</v>
       </c>
       <c r="C150" s="4">
@@ -24595,11 +25106,11 @@
       </c>
       <c r="S150" s="1"/>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A151" s="3">
+    <row r="151" spans="1:19">
+      <c r="A151" s="13">
         <v>45950</v>
       </c>
-      <c r="B151" s="3">
+      <c r="B151" s="13">
         <v>45950</v>
       </c>
       <c r="C151" s="4">
@@ -24652,11 +25163,11 @@
       </c>
       <c r="S151" s="1"/>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A152" s="3">
+    <row r="152" spans="1:19">
+      <c r="A152" s="13">
         <v>45957</v>
       </c>
-      <c r="B152" s="3">
+      <c r="B152" s="13">
         <v>45957</v>
       </c>
       <c r="C152" s="4">
@@ -24709,11 +25220,11 @@
       </c>
       <c r="S152" s="1"/>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A153" s="3">
+    <row r="153" spans="1:19">
+      <c r="A153" s="13">
         <v>45964</v>
       </c>
-      <c r="B153" s="3">
+      <c r="B153" s="13">
         <v>45964</v>
       </c>
       <c r="C153" s="4">
@@ -24766,11 +25277,11 @@
       </c>
       <c r="S153" s="1"/>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A154" s="3">
+    <row r="154" spans="1:19">
+      <c r="A154" s="13">
         <v>45971</v>
       </c>
-      <c r="B154" s="3">
+      <c r="B154" s="13">
         <v>45971</v>
       </c>
       <c r="C154" s="4">
@@ -24823,11 +25334,11 @@
       </c>
       <c r="S154" s="1"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A155" s="3">
+    <row r="155" spans="1:19">
+      <c r="A155" s="13">
         <v>45978</v>
       </c>
-      <c r="B155" s="3">
+      <c r="B155" s="13">
         <v>45978</v>
       </c>
       <c r="C155" s="4">
@@ -24880,11 +25391,11 @@
       </c>
       <c r="S155" s="1"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A156" s="3">
+    <row r="156" spans="1:19">
+      <c r="A156" s="13">
         <v>45985</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B156" s="13">
         <v>45985</v>
       </c>
       <c r="C156" s="4">
@@ -24937,11 +25448,11 @@
       </c>
       <c r="S156" s="1"/>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A157" s="3">
+    <row r="157" spans="1:19">
+      <c r="A157" s="13">
         <v>45992</v>
       </c>
-      <c r="B157" s="3">
+      <c r="B157" s="13">
         <v>45992</v>
       </c>
       <c r="C157" s="4">
@@ -24994,11 +25505,11 @@
       </c>
       <c r="S157" s="1"/>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
+    <row r="158" spans="1:19">
+      <c r="A158" s="13">
         <v>45999</v>
       </c>
-      <c r="B158" s="3">
+      <c r="B158" s="13">
         <v>45999</v>
       </c>
       <c r="C158" s="4">
@@ -25051,11 +25562,11 @@
       </c>
       <c r="S158" s="1"/>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A159" s="3">
+    <row r="159" spans="1:19">
+      <c r="A159" s="13">
         <v>46006</v>
       </c>
-      <c r="B159" s="3">
+      <c r="B159" s="13">
         <v>46006</v>
       </c>
       <c r="C159" s="4">
@@ -25108,11 +25619,11 @@
       </c>
       <c r="S159" s="1"/>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A160" s="3">
+    <row r="160" spans="1:19">
+      <c r="A160" s="13">
         <v>46013</v>
       </c>
-      <c r="B160" s="3">
+      <c r="B160" s="13">
         <v>46013</v>
       </c>
       <c r="C160" s="4">
@@ -25165,11 +25676,11 @@
       </c>
       <c r="S160" s="1"/>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A161" s="3">
+    <row r="161" spans="1:19">
+      <c r="A161" s="13">
         <v>46020</v>
       </c>
-      <c r="B161" s="3">
+      <c r="B161" s="13">
         <v>46020</v>
       </c>
       <c r="C161" s="4">
@@ -25222,11 +25733,11 @@
       </c>
       <c r="S161" s="1"/>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A162" s="3">
+    <row r="162" spans="1:19">
+      <c r="A162" s="13">
         <v>46034</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162" s="13">
         <v>46034</v>
       </c>
       <c r="C162" s="4">
@@ -25279,11 +25790,11 @@
       </c>
       <c r="S162" s="1"/>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A163" s="3">
+    <row r="163" spans="1:19">
+      <c r="A163" s="13">
         <v>46041</v>
       </c>
-      <c r="B163" s="3">
+      <c r="B163" s="13">
         <v>46041</v>
       </c>
       <c r="C163" s="4">
@@ -25336,11 +25847,11 @@
       </c>
       <c r="S163" s="1"/>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A164" s="3">
+    <row r="164" spans="1:19">
+      <c r="A164" s="13">
         <v>46048</v>
       </c>
-      <c r="B164" s="3">
+      <c r="B164" s="13">
         <v>46048</v>
       </c>
       <c r="C164" s="4">
@@ -25393,11 +25904,11 @@
       </c>
       <c r="S164" s="1"/>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A165" s="3">
+    <row r="165" spans="1:19">
+      <c r="A165" s="13">
         <v>46055</v>
       </c>
-      <c r="B165" s="3">
+      <c r="B165" s="13">
         <v>46055</v>
       </c>
       <c r="C165" s="4">
@@ -25450,11 +25961,11 @@
       </c>
       <c r="S165" s="1"/>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A166" s="3">
+    <row r="166" spans="1:19">
+      <c r="A166" s="13">
         <v>46062</v>
       </c>
-      <c r="B166" s="3">
+      <c r="B166" s="13">
         <v>46062</v>
       </c>
       <c r="C166" s="4">
@@ -25507,11 +26018,11 @@
       </c>
       <c r="S166" s="1"/>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A167" s="3">
+    <row r="167" spans="1:19">
+      <c r="A167" s="13">
         <v>46076</v>
       </c>
-      <c r="B167" s="3">
+      <c r="B167" s="13">
         <v>46076</v>
       </c>
       <c r="C167" s="4">
@@ -25563,11 +26074,11 @@
         <v>886</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A168" s="3">
+    <row r="168" spans="1:19">
+      <c r="A168" s="13">
         <v>46084</v>
       </c>
-      <c r="B168" s="3">
+      <c r="B168" s="13">
         <v>46084</v>
       </c>
       <c r="C168" s="4">
@@ -25619,11 +26130,11 @@
         <v>876</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A169" s="3">
+    <row r="169" spans="1:19">
+      <c r="A169" s="13">
         <v>46090</v>
       </c>
-      <c r="B169" s="3">
+      <c r="B169" s="13">
         <v>46090</v>
       </c>
       <c r="C169" s="4">
@@ -25675,11 +26186,11 @@
         <v>865</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A170" s="3">
+    <row r="170" spans="1:19">
+      <c r="A170" s="13">
         <v>46097</v>
       </c>
-      <c r="B170" s="3">
+      <c r="B170" s="13">
         <v>46097</v>
       </c>
       <c r="C170" s="4">
@@ -25731,12 +26242,12 @@
         <v>902</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A171" s="3">
-        <v>46084</v>
-      </c>
-      <c r="B171" s="3">
-        <v>46084</v>
+    <row r="171" spans="1:19">
+      <c r="A171" s="13">
+        <v>46104</v>
+      </c>
+      <c r="B171" s="13">
+        <v>46104</v>
       </c>
       <c r="C171" s="4">
         <v>0.58333333333333304</v>
@@ -25787,8 +26298,64 @@
         <v>998</v>
       </c>
     </row>
+    <row r="172" spans="1:19">
+      <c r="A172" s="13">
+        <v>46111</v>
+      </c>
+      <c r="B172" s="13">
+        <v>46111</v>
+      </c>
+      <c r="C172" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E172" s="7">
+        <v>2094</v>
+      </c>
+      <c r="F172" s="7">
+        <v>2362</v>
+      </c>
+      <c r="G172" s="7">
+        <v>3196</v>
+      </c>
+      <c r="H172" s="7">
+        <v>2718</v>
+      </c>
+      <c r="I172" s="7">
+        <v>3896</v>
+      </c>
+      <c r="J172" s="7">
+        <v>5394</v>
+      </c>
+      <c r="K172" s="7">
+        <v>1518</v>
+      </c>
+      <c r="L172" s="7">
+        <v>3033</v>
+      </c>
+      <c r="M172" s="7">
+        <v>2884</v>
+      </c>
+      <c r="N172" s="7">
+        <v>3008</v>
+      </c>
+      <c r="O172" s="7">
+        <v>4027</v>
+      </c>
+      <c r="P172" s="7">
+        <v>58</v>
+      </c>
+      <c r="Q172" s="7">
+        <v>238</v>
+      </c>
+      <c r="R172" s="7">
+        <v>1024</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A3:R166">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:R166">
     <sortCondition ref="A3:A166"/>
   </sortState>
   <mergeCells count="4">
@@ -25806,14 +26373,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EF7E42-3273-4C27-80E3-741AD2FB330F}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="2" max="2" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="16">
       <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
@@ -25821,7 +26388,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
         <v>34</v>
       </c>
@@ -25842,9 +26409,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BD5038-94A8-4C07-9E87-4FDF24EEDBD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F14890-6CEC-46DA-8353-D1F6D18EF0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FB7481-6E1C-461C-94FE-3245F673C0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -173,7 +173,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -277,16 +277,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -873,6 +873,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1391,6 +1394,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>2178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1947,6 +1953,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2465,6 +2474,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>2362</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>2467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3021,6 +3033,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3539,6 +3554,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>3196</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3406</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4095,6 +4113,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4613,6 +4634,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>2718</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>2646</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5169,6 +5193,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5687,6 +5714,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>3896</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3730</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6243,6 +6273,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6761,6 +6794,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>5394</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>6211</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7319,6 +7355,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7837,6 +7876,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>1518</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1509</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8395,6 +8437,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8913,6 +8958,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>3033</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9471,6 +9519,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9989,6 +10040,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>2884</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3089</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10547,6 +10601,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11065,6 +11122,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>3008</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>2984</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11623,6 +11683,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12141,6 +12204,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>4027</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4068</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12715,6 +12781,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13233,6 +13302,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13792,6 +13864,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14310,6 +14385,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14869,6 +14947,9 @@
                 <c:pt idx="169">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="170">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15387,6 +15468,9 @@
                 </c:pt>
                 <c:pt idx="169">
                   <c:v>1024</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1070</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16554,11 +16638,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S172"/>
+  <dimension ref="A1:S173"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.1796875" style="4" customWidth="1"/>
     <col min="4" max="4" width="13.1796875" style="3" customWidth="1"/>
     <col min="5" max="18" width="12.81640625" style="7" customWidth="1"/>
@@ -16567,16 +16651,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -16623,10 +16707,10 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
@@ -16671,10 +16755,10 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="13">
+      <c r="A3" s="10">
         <v>44872</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="10">
         <v>44872</v>
       </c>
       <c r="C3" s="4">
@@ -16728,10 +16812,10 @@
       <c r="S3" s="1"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="13">
+      <c r="A4" s="10">
         <v>44879</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="10">
         <v>44879</v>
       </c>
       <c r="C4" s="4">
@@ -16785,10 +16869,10 @@
       <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="13">
+      <c r="A5" s="10">
         <v>44886</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="10">
         <v>44886</v>
       </c>
       <c r="C5" s="4">
@@ -16842,10 +16926,10 @@
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="13">
+      <c r="A6" s="10">
         <v>44893</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="10">
         <v>44893</v>
       </c>
       <c r="C6" s="4">
@@ -16899,10 +16983,10 @@
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="13">
+      <c r="A7" s="10">
         <v>44900</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="10">
         <v>44900</v>
       </c>
       <c r="C7" s="4">
@@ -16956,10 +17040,10 @@
       <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="13">
+      <c r="A8" s="10">
         <v>44907</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="10">
         <v>44907</v>
       </c>
       <c r="C8" s="4">
@@ -17013,10 +17097,10 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="13">
+      <c r="A9" s="10">
         <v>44914</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="10">
         <v>44914</v>
       </c>
       <c r="C9" s="4">
@@ -17070,10 +17154,10 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="13">
+      <c r="A10" s="10">
         <v>44921</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="10">
         <v>44921</v>
       </c>
       <c r="C10" s="4">
@@ -17127,10 +17211,10 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="13">
+      <c r="A11" s="10">
         <v>44928</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="10">
         <v>44928</v>
       </c>
       <c r="C11" s="4">
@@ -17184,10 +17268,10 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="13">
+      <c r="A12" s="10">
         <v>44935</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="10">
         <v>44935</v>
       </c>
       <c r="C12" s="4">
@@ -17241,10 +17325,10 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="13">
+      <c r="A13" s="10">
         <v>44942</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="10">
         <v>44942</v>
       </c>
       <c r="C13" s="4">
@@ -17298,10 +17382,10 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="13">
+      <c r="A14" s="10">
         <v>44951</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="10">
         <v>44951</v>
       </c>
       <c r="C14" s="4">
@@ -17355,10 +17439,10 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="13">
+      <c r="A15" s="10">
         <v>44956</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="10">
         <v>44956</v>
       </c>
       <c r="C15" s="4">
@@ -17412,10 +17496,10 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="13">
+      <c r="A16" s="10">
         <v>44963</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="10">
         <v>44963</v>
       </c>
       <c r="C16" s="4">
@@ -17469,10 +17553,10 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="13">
+      <c r="A17" s="10">
         <v>44970</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="10">
         <v>44970</v>
       </c>
       <c r="C17" s="4">
@@ -17526,10 +17610,10 @@
       <c r="S17" s="1"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="13">
+      <c r="A18" s="10">
         <v>44977</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="10">
         <v>44977</v>
       </c>
       <c r="C18" s="4">
@@ -17583,10 +17667,10 @@
       <c r="S18" s="1"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="13">
+      <c r="A19" s="10">
         <v>44984</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="10">
         <v>44984</v>
       </c>
       <c r="C19" s="4">
@@ -17640,10 +17724,10 @@
       <c r="S19" s="1"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="13">
+      <c r="A20" s="10">
         <v>44991</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="10">
         <v>44991</v>
       </c>
       <c r="C20" s="4">
@@ -17697,10 +17781,10 @@
       <c r="S20" s="1"/>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="13">
+      <c r="A21" s="10">
         <v>44998</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <v>44998</v>
       </c>
       <c r="C21" s="4">
@@ -17754,10 +17838,10 @@
       <c r="S21" s="1"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="13">
+      <c r="A22" s="10">
         <v>45005</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <v>45005</v>
       </c>
       <c r="C22" s="4">
@@ -17811,10 +17895,10 @@
       <c r="S22" s="1"/>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="13">
+      <c r="A23" s="10">
         <v>45012</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <v>45012</v>
       </c>
       <c r="C23" s="4">
@@ -17868,10 +17952,10 @@
       <c r="S23" s="1"/>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="13">
+      <c r="A24" s="10">
         <v>45019</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="10">
         <v>45019</v>
       </c>
       <c r="C24" s="4">
@@ -17925,10 +18009,10 @@
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="13">
+      <c r="A25" s="10">
         <v>45026</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="10">
         <v>45026</v>
       </c>
       <c r="C25" s="4">
@@ -17982,10 +18066,10 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="13">
+      <c r="A26" s="10">
         <v>45033</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <v>45033</v>
       </c>
       <c r="C26" s="4">
@@ -18039,10 +18123,10 @@
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="13">
+      <c r="A27" s="10">
         <v>45040</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="10">
         <v>45040</v>
       </c>
       <c r="C27" s="4">
@@ -18096,10 +18180,10 @@
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="13">
+      <c r="A28" s="10">
         <v>45048</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="10">
         <v>45048</v>
       </c>
       <c r="C28" s="4">
@@ -18153,10 +18237,10 @@
       <c r="S28" s="1"/>
     </row>
     <row r="29" spans="1:19">
-      <c r="A29" s="13">
+      <c r="A29" s="10">
         <v>45054</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="10">
         <v>45054</v>
       </c>
       <c r="C29" s="4">
@@ -18210,10 +18294,10 @@
       <c r="S29" s="1"/>
     </row>
     <row r="30" spans="1:19">
-      <c r="A30" s="13">
+      <c r="A30" s="10">
         <v>45061</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="10">
         <v>45061</v>
       </c>
       <c r="C30" s="4">
@@ -18267,10 +18351,10 @@
       <c r="S30" s="1"/>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="13">
+      <c r="A31" s="10">
         <v>45068</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="10">
         <v>45068</v>
       </c>
       <c r="C31" s="4">
@@ -18324,10 +18408,10 @@
       <c r="S31" s="1"/>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="13">
+      <c r="A32" s="10">
         <v>45076</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="10">
         <v>45076</v>
       </c>
       <c r="C32" s="4">
@@ -18381,10 +18465,10 @@
       <c r="S32" s="1"/>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="13">
+      <c r="A33" s="10">
         <v>45082</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="10">
         <v>45082</v>
       </c>
       <c r="C33" s="4">
@@ -18438,10 +18522,10 @@
       <c r="S33" s="1"/>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="13">
+      <c r="A34" s="10">
         <v>45089</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="10">
         <v>45089</v>
       </c>
       <c r="C34" s="4">
@@ -18495,10 +18579,10 @@
       <c r="S34" s="1"/>
     </row>
     <row r="35" spans="1:19">
-      <c r="A35" s="13">
+      <c r="A35" s="10">
         <v>45096</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="10">
         <v>45096</v>
       </c>
       <c r="C35" s="4">
@@ -18552,10 +18636,10 @@
       <c r="S35" s="1"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="13">
+      <c r="A36" s="10">
         <v>45103</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="10">
         <v>45103</v>
       </c>
       <c r="C36" s="4">
@@ -18609,10 +18693,10 @@
       <c r="S36" s="1"/>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="13">
+      <c r="A37" s="10">
         <v>45110</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="10">
         <v>45110</v>
       </c>
       <c r="C37" s="4">
@@ -18666,10 +18750,10 @@
       <c r="S37" s="1"/>
     </row>
     <row r="38" spans="1:19">
-      <c r="A38" s="13">
+      <c r="A38" s="10">
         <v>45117</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="10">
         <v>45117</v>
       </c>
       <c r="C38" s="4">
@@ -18723,10 +18807,10 @@
       <c r="S38" s="1"/>
     </row>
     <row r="39" spans="1:19">
-      <c r="A39" s="13">
+      <c r="A39" s="10">
         <v>45124</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="10">
         <v>45124</v>
       </c>
       <c r="C39" s="4">
@@ -18780,10 +18864,10 @@
       <c r="S39" s="1"/>
     </row>
     <row r="40" spans="1:19">
-      <c r="A40" s="13">
+      <c r="A40" s="10">
         <v>45131</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="10">
         <v>45131</v>
       </c>
       <c r="C40" s="4">
@@ -18837,10 +18921,10 @@
       <c r="S40" s="1"/>
     </row>
     <row r="41" spans="1:19">
-      <c r="A41" s="13">
+      <c r="A41" s="10">
         <v>45138</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="10">
         <v>45138</v>
       </c>
       <c r="C41" s="4">
@@ -18894,10 +18978,10 @@
       <c r="S41" s="1"/>
     </row>
     <row r="42" spans="1:19">
-      <c r="A42" s="13">
+      <c r="A42" s="10">
         <v>45145</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="10">
         <v>45145</v>
       </c>
       <c r="C42" s="4">
@@ -18951,10 +19035,10 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19">
-      <c r="A43" s="13">
+      <c r="A43" s="10">
         <v>45152</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="10">
         <v>45152</v>
       </c>
       <c r="C43" s="4">
@@ -19008,10 +19092,10 @@
       <c r="S43" s="1"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="13">
+      <c r="A44" s="10">
         <v>45159</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="10">
         <v>45159</v>
       </c>
       <c r="C44" s="4">
@@ -19065,10 +19149,10 @@
       <c r="S44" s="1"/>
     </row>
     <row r="45" spans="1:19">
-      <c r="A45" s="13">
+      <c r="A45" s="10">
         <v>45166</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="10">
         <v>45166</v>
       </c>
       <c r="C45" s="4">
@@ -19122,10 +19206,10 @@
       <c r="S45" s="1"/>
     </row>
     <row r="46" spans="1:19">
-      <c r="A46" s="13">
+      <c r="A46" s="10">
         <v>45173</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="10">
         <v>45173</v>
       </c>
       <c r="C46" s="4">
@@ -19179,10 +19263,10 @@
       <c r="S46" s="1"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="13">
+      <c r="A47" s="10">
         <v>45180</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="10">
         <v>45180</v>
       </c>
       <c r="C47" s="4">
@@ -19236,10 +19320,10 @@
       <c r="S47" s="1"/>
     </row>
     <row r="48" spans="1:19">
-      <c r="A48" s="13">
+      <c r="A48" s="10">
         <v>45187</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="10">
         <v>45187</v>
       </c>
       <c r="C48" s="4">
@@ -19293,10 +19377,10 @@
       <c r="S48" s="1"/>
     </row>
     <row r="49" spans="1:19">
-      <c r="A49" s="13">
+      <c r="A49" s="10">
         <v>45194</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="10">
         <v>45194</v>
       </c>
       <c r="C49" s="4">
@@ -19350,10 +19434,10 @@
       <c r="S49" s="1"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="13">
+      <c r="A50" s="10">
         <v>45209</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="10">
         <v>45209</v>
       </c>
       <c r="C50" s="4">
@@ -19407,10 +19491,10 @@
       <c r="S50" s="1"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="13">
+      <c r="A51" s="10">
         <v>45215</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="10">
         <v>45215</v>
       </c>
       <c r="C51" s="4">
@@ -19464,10 +19548,10 @@
       <c r="S51" s="1"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="13">
+      <c r="A52" s="10">
         <v>45222</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="10">
         <v>45222</v>
       </c>
       <c r="C52" s="4">
@@ -19521,10 +19605,10 @@
       <c r="S52" s="1"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="13">
+      <c r="A53" s="10">
         <v>45229</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="10">
         <v>45229</v>
       </c>
       <c r="C53" s="4">
@@ -19578,10 +19662,10 @@
       <c r="S53" s="1"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="13">
+      <c r="A54" s="10">
         <v>45236</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="10">
         <v>45236</v>
       </c>
       <c r="C54" s="4">
@@ -19635,10 +19719,10 @@
       <c r="S54" s="1"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="13">
+      <c r="A55" s="10">
         <v>45243</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="10">
         <v>45243</v>
       </c>
       <c r="C55" s="4">
@@ -19692,10 +19776,10 @@
       <c r="S55" s="1"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="13">
+      <c r="A56" s="10">
         <v>45250</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="10">
         <v>45250</v>
       </c>
       <c r="C56" s="4">
@@ -19749,10 +19833,10 @@
       <c r="S56" s="1"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="13">
+      <c r="A57" s="10">
         <v>45257</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="10">
         <v>45257</v>
       </c>
       <c r="C57" s="4">
@@ -19806,10 +19890,10 @@
       <c r="S57" s="1"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="13">
+      <c r="A58" s="10">
         <v>45264</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="10">
         <v>45264</v>
       </c>
       <c r="C58" s="4">
@@ -19863,10 +19947,10 @@
       <c r="S58" s="1"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="13">
+      <c r="A59" s="10">
         <v>45271</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="10">
         <v>45271</v>
       </c>
       <c r="C59" s="4">
@@ -19920,10 +20004,10 @@
       <c r="S59" s="1"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="13">
+      <c r="A60" s="10">
         <v>45278</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="10">
         <v>45278</v>
       </c>
       <c r="C60" s="4">
@@ -19977,10 +20061,10 @@
       <c r="S60" s="1"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="13">
+      <c r="A61" s="10">
         <v>45286</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="10">
         <v>45286</v>
       </c>
       <c r="C61" s="4">
@@ -20034,10 +20118,10 @@
       <c r="S61" s="1"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="13">
+      <c r="A62" s="10">
         <v>45293</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="10">
         <v>45293</v>
       </c>
       <c r="C62" s="4">
@@ -20091,10 +20175,10 @@
       <c r="S62" s="1"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="13">
+      <c r="A63" s="10">
         <v>45299</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="10">
         <v>45299</v>
       </c>
       <c r="C63" s="4">
@@ -20148,10 +20232,10 @@
       <c r="S63" s="1"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="13">
+      <c r="A64" s="10">
         <v>45306</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="10">
         <v>45306</v>
       </c>
       <c r="C64" s="4">
@@ -20205,10 +20289,10 @@
       <c r="S64" s="1"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="13">
+      <c r="A65" s="10">
         <v>45313</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="10">
         <v>45313</v>
       </c>
       <c r="C65" s="4">
@@ -20262,10 +20346,10 @@
       <c r="S65" s="1"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="13">
+      <c r="A66" s="10">
         <v>45320</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="10">
         <v>45320</v>
       </c>
       <c r="C66" s="4">
@@ -20319,10 +20403,10 @@
       <c r="S66" s="1"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="13">
+      <c r="A67" s="10">
         <v>45327</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="10">
         <v>45327</v>
       </c>
       <c r="C67" s="4">
@@ -20376,10 +20460,10 @@
       <c r="S67" s="1"/>
     </row>
     <row r="68" spans="1:19">
-      <c r="A68" s="13">
+      <c r="A68" s="10">
         <v>45335</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="10">
         <v>45335</v>
       </c>
       <c r="C68" s="4">
@@ -20433,10 +20517,10 @@
       <c r="S68" s="1"/>
     </row>
     <row r="69" spans="1:19">
-      <c r="A69" s="13">
+      <c r="A69" s="10">
         <v>45341</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="10">
         <v>45341</v>
       </c>
       <c r="C69" s="4">
@@ -20490,10 +20574,10 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19">
-      <c r="A70" s="13">
+      <c r="A70" s="10">
         <v>45348</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="10">
         <v>45348</v>
       </c>
       <c r="C70" s="4">
@@ -20547,10 +20631,10 @@
       <c r="S70" s="1"/>
     </row>
     <row r="71" spans="1:19">
-      <c r="A71" s="13">
+      <c r="A71" s="10">
         <v>45355</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="10">
         <v>45355</v>
       </c>
       <c r="C71" s="4">
@@ -20604,10 +20688,10 @@
       <c r="S71" s="1"/>
     </row>
     <row r="72" spans="1:19">
-      <c r="A72" s="13">
+      <c r="A72" s="10">
         <v>45362</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="10">
         <v>45362</v>
       </c>
       <c r="C72" s="4">
@@ -20661,10 +20745,10 @@
       <c r="S72" s="1"/>
     </row>
     <row r="73" spans="1:19">
-      <c r="A73" s="13">
+      <c r="A73" s="10">
         <v>45369</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="10">
         <v>45369</v>
       </c>
       <c r="C73" s="4">
@@ -20718,10 +20802,10 @@
       <c r="S73" s="1"/>
     </row>
     <row r="74" spans="1:19">
-      <c r="A74" s="13">
+      <c r="A74" s="10">
         <v>45376</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="10">
         <v>45376</v>
       </c>
       <c r="C74" s="4">
@@ -20775,10 +20859,10 @@
       <c r="S74" s="1"/>
     </row>
     <row r="75" spans="1:19">
-      <c r="A75" s="13">
+      <c r="A75" s="10">
         <v>45383</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="10">
         <v>45383</v>
       </c>
       <c r="C75" s="4">
@@ -20832,10 +20916,10 @@
       <c r="S75" s="1"/>
     </row>
     <row r="76" spans="1:19">
-      <c r="A76" s="13">
+      <c r="A76" s="10">
         <v>45390</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="10">
         <v>45390</v>
       </c>
       <c r="C76" s="4">
@@ -20889,10 +20973,10 @@
       <c r="S76" s="1"/>
     </row>
     <row r="77" spans="1:19">
-      <c r="A77" s="13">
+      <c r="A77" s="10">
         <v>45397</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="10">
         <v>45397</v>
       </c>
       <c r="C77" s="4">
@@ -20946,10 +21030,10 @@
       <c r="S77" s="1"/>
     </row>
     <row r="78" spans="1:19">
-      <c r="A78" s="13">
+      <c r="A78" s="10">
         <v>45404</v>
       </c>
-      <c r="B78" s="13">
+      <c r="B78" s="10">
         <v>45404</v>
       </c>
       <c r="C78" s="4">
@@ -21003,10 +21087,10 @@
       <c r="S78" s="1"/>
     </row>
     <row r="79" spans="1:19">
-      <c r="A79" s="13">
+      <c r="A79" s="10">
         <v>45411</v>
       </c>
-      <c r="B79" s="13">
+      <c r="B79" s="10">
         <v>45411</v>
       </c>
       <c r="C79" s="4">
@@ -21060,10 +21144,10 @@
       <c r="S79" s="1"/>
     </row>
     <row r="80" spans="1:19">
-      <c r="A80" s="13">
+      <c r="A80" s="10">
         <v>45419</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="10">
         <v>45419</v>
       </c>
       <c r="C80" s="4">
@@ -21117,10 +21201,10 @@
       <c r="S80" s="1"/>
     </row>
     <row r="81" spans="1:19">
-      <c r="A81" s="13">
+      <c r="A81" s="10">
         <v>45425</v>
       </c>
-      <c r="B81" s="13">
+      <c r="B81" s="10">
         <v>45425</v>
       </c>
       <c r="C81" s="4">
@@ -21174,10 +21258,10 @@
       <c r="S81" s="1"/>
     </row>
     <row r="82" spans="1:19">
-      <c r="A82" s="13">
+      <c r="A82" s="10">
         <v>45432</v>
       </c>
-      <c r="B82" s="13">
+      <c r="B82" s="10">
         <v>45432</v>
       </c>
       <c r="C82" s="4">
@@ -21231,10 +21315,10 @@
       <c r="S82" s="1"/>
     </row>
     <row r="83" spans="1:19">
-      <c r="A83" s="13">
+      <c r="A83" s="10">
         <v>45439</v>
       </c>
-      <c r="B83" s="13">
+      <c r="B83" s="10">
         <v>45439</v>
       </c>
       <c r="C83" s="4">
@@ -21288,10 +21372,10 @@
       <c r="S83" s="1"/>
     </row>
     <row r="84" spans="1:19">
-      <c r="A84" s="13">
+      <c r="A84" s="10">
         <v>45446</v>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="10">
         <v>45446</v>
       </c>
       <c r="C84" s="4">
@@ -21345,10 +21429,10 @@
       <c r="S84" s="1"/>
     </row>
     <row r="85" spans="1:19">
-      <c r="A85" s="13">
+      <c r="A85" s="10">
         <v>45453</v>
       </c>
-      <c r="B85" s="13">
+      <c r="B85" s="10">
         <v>45453</v>
       </c>
       <c r="C85" s="4">
@@ -21402,10 +21486,10 @@
       <c r="S85" s="1"/>
     </row>
     <row r="86" spans="1:19">
-      <c r="A86" s="13">
+      <c r="A86" s="10">
         <v>45460</v>
       </c>
-      <c r="B86" s="13">
+      <c r="B86" s="10">
         <v>45460</v>
       </c>
       <c r="C86" s="4">
@@ -21459,10 +21543,10 @@
       <c r="S86" s="1"/>
     </row>
     <row r="87" spans="1:19">
-      <c r="A87" s="13">
+      <c r="A87" s="10">
         <v>45467</v>
       </c>
-      <c r="B87" s="13">
+      <c r="B87" s="10">
         <v>45467</v>
       </c>
       <c r="C87" s="4">
@@ -21516,10 +21600,10 @@
       <c r="S87" s="1"/>
     </row>
     <row r="88" spans="1:19">
-      <c r="A88" s="13">
+      <c r="A88" s="10">
         <v>45474</v>
       </c>
-      <c r="B88" s="13">
+      <c r="B88" s="10">
         <v>45474</v>
       </c>
       <c r="C88" s="4">
@@ -21573,10 +21657,10 @@
       <c r="S88" s="1"/>
     </row>
     <row r="89" spans="1:19">
-      <c r="A89" s="13">
+      <c r="A89" s="10">
         <v>45481</v>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="10">
         <v>45481</v>
       </c>
       <c r="C89" s="4">
@@ -21630,10 +21714,10 @@
       <c r="S89" s="1"/>
     </row>
     <row r="90" spans="1:19">
-      <c r="A90" s="13">
+      <c r="A90" s="10">
         <v>45488</v>
       </c>
-      <c r="B90" s="13">
+      <c r="B90" s="10">
         <v>45488</v>
       </c>
       <c r="C90" s="4">
@@ -21687,10 +21771,10 @@
       <c r="S90" s="1"/>
     </row>
     <row r="91" spans="1:19">
-      <c r="A91" s="13">
+      <c r="A91" s="10">
         <v>45495</v>
       </c>
-      <c r="B91" s="13">
+      <c r="B91" s="10">
         <v>45495</v>
       </c>
       <c r="C91" s="4">
@@ -21744,10 +21828,10 @@
       <c r="S91" s="1"/>
     </row>
     <row r="92" spans="1:19">
-      <c r="A92" s="13">
+      <c r="A92" s="10">
         <v>45502</v>
       </c>
-      <c r="B92" s="13">
+      <c r="B92" s="10">
         <v>45502</v>
       </c>
       <c r="C92" s="4">
@@ -21801,10 +21885,10 @@
       <c r="S92" s="1"/>
     </row>
     <row r="93" spans="1:19">
-      <c r="A93" s="13">
+      <c r="A93" s="10">
         <v>45509</v>
       </c>
-      <c r="B93" s="13">
+      <c r="B93" s="10">
         <v>45509</v>
       </c>
       <c r="C93" s="4">
@@ -21858,10 +21942,10 @@
       <c r="S93" s="1"/>
     </row>
     <row r="94" spans="1:19">
-      <c r="A94" s="13">
+      <c r="A94" s="10">
         <v>45516</v>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="10">
         <v>45516</v>
       </c>
       <c r="C94" s="4">
@@ -21915,10 +21999,10 @@
       <c r="S94" s="1"/>
     </row>
     <row r="95" spans="1:19">
-      <c r="A95" s="13">
+      <c r="A95" s="10">
         <v>45523</v>
       </c>
-      <c r="B95" s="13">
+      <c r="B95" s="10">
         <v>45523</v>
       </c>
       <c r="C95" s="4">
@@ -21972,10 +22056,10 @@
       <c r="S95" s="1"/>
     </row>
     <row r="96" spans="1:19">
-      <c r="A96" s="13">
+      <c r="A96" s="10">
         <v>45530</v>
       </c>
-      <c r="B96" s="13">
+      <c r="B96" s="10">
         <v>45530</v>
       </c>
       <c r="C96" s="4">
@@ -22029,10 +22113,10 @@
       <c r="S96" s="1"/>
     </row>
     <row r="97" spans="1:19">
-      <c r="A97" s="13">
+      <c r="A97" s="10">
         <v>45537</v>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="10">
         <v>45537</v>
       </c>
       <c r="C97" s="4">
@@ -22086,10 +22170,10 @@
       <c r="S97" s="1"/>
     </row>
     <row r="98" spans="1:19">
-      <c r="A98" s="13">
+      <c r="A98" s="10">
         <v>45544</v>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="10">
         <v>45544</v>
       </c>
       <c r="C98" s="4">
@@ -22143,10 +22227,10 @@
       <c r="S98" s="1"/>
     </row>
     <row r="99" spans="1:19">
-      <c r="A99" s="13">
+      <c r="A99" s="10">
         <v>45558</v>
       </c>
-      <c r="B99" s="13">
+      <c r="B99" s="10">
         <v>45558</v>
       </c>
       <c r="C99" s="4">
@@ -22200,10 +22284,10 @@
       <c r="S99" s="1"/>
     </row>
     <row r="100" spans="1:19">
-      <c r="A100" s="13">
+      <c r="A100" s="10">
         <v>45565</v>
       </c>
-      <c r="B100" s="13">
+      <c r="B100" s="10">
         <v>45565</v>
       </c>
       <c r="C100" s="4">
@@ -22257,10 +22341,10 @@
       <c r="S100" s="1"/>
     </row>
     <row r="101" spans="1:19">
-      <c r="A101" s="13">
+      <c r="A101" s="10">
         <v>45572</v>
       </c>
-      <c r="B101" s="13">
+      <c r="B101" s="10">
         <v>45572</v>
       </c>
       <c r="C101" s="4">
@@ -22314,10 +22398,10 @@
       <c r="S101" s="1"/>
     </row>
     <row r="102" spans="1:19">
-      <c r="A102" s="13">
+      <c r="A102" s="10">
         <v>45579</v>
       </c>
-      <c r="B102" s="13">
+      <c r="B102" s="10">
         <v>45579</v>
       </c>
       <c r="C102" s="4">
@@ -22371,10 +22455,10 @@
       <c r="S102" s="1"/>
     </row>
     <row r="103" spans="1:19">
-      <c r="A103" s="13">
+      <c r="A103" s="10">
         <v>45586</v>
       </c>
-      <c r="B103" s="13">
+      <c r="B103" s="10">
         <v>45586</v>
       </c>
       <c r="C103" s="4">
@@ -22428,10 +22512,10 @@
       <c r="S103" s="1"/>
     </row>
     <row r="104" spans="1:19">
-      <c r="A104" s="13">
+      <c r="A104" s="10">
         <v>45593</v>
       </c>
-      <c r="B104" s="13">
+      <c r="B104" s="10">
         <v>45593</v>
       </c>
       <c r="C104" s="4">
@@ -22485,10 +22569,10 @@
       <c r="S104" s="1"/>
     </row>
     <row r="105" spans="1:19">
-      <c r="A105" s="13">
+      <c r="A105" s="10">
         <v>45600</v>
       </c>
-      <c r="B105" s="13">
+      <c r="B105" s="10">
         <v>45600</v>
       </c>
       <c r="C105" s="4">
@@ -22542,10 +22626,10 @@
       <c r="S105" s="1"/>
     </row>
     <row r="106" spans="1:19">
-      <c r="A106" s="13">
+      <c r="A106" s="10">
         <v>45607</v>
       </c>
-      <c r="B106" s="13">
+      <c r="B106" s="10">
         <v>45607</v>
       </c>
       <c r="C106" s="4">
@@ -22599,10 +22683,10 @@
       <c r="S106" s="1"/>
     </row>
     <row r="107" spans="1:19">
-      <c r="A107" s="13">
+      <c r="A107" s="10">
         <v>45614</v>
       </c>
-      <c r="B107" s="13">
+      <c r="B107" s="10">
         <v>45614</v>
       </c>
       <c r="C107" s="4">
@@ -22656,10 +22740,10 @@
       <c r="S107" s="1"/>
     </row>
     <row r="108" spans="1:19">
-      <c r="A108" s="13">
+      <c r="A108" s="10">
         <v>45621</v>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="10">
         <v>45621</v>
       </c>
       <c r="C108" s="4">
@@ -22713,10 +22797,10 @@
       <c r="S108" s="1"/>
     </row>
     <row r="109" spans="1:19">
-      <c r="A109" s="13">
+      <c r="A109" s="10">
         <v>45628</v>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="10">
         <v>45628</v>
       </c>
       <c r="C109" s="4">
@@ -22770,10 +22854,10 @@
       <c r="S109" s="1"/>
     </row>
     <row r="110" spans="1:19">
-      <c r="A110" s="13">
+      <c r="A110" s="10">
         <v>45635</v>
       </c>
-      <c r="B110" s="13">
+      <c r="B110" s="10">
         <v>45635</v>
       </c>
       <c r="C110" s="4">
@@ -22827,10 +22911,10 @@
       <c r="S110" s="1"/>
     </row>
     <row r="111" spans="1:19">
-      <c r="A111" s="13">
+      <c r="A111" s="10">
         <v>45642</v>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="10">
         <v>45642</v>
       </c>
       <c r="C111" s="4">
@@ -22884,10 +22968,10 @@
       <c r="S111" s="1"/>
     </row>
     <row r="112" spans="1:19">
-      <c r="A112" s="13">
+      <c r="A112" s="10">
         <v>45649</v>
       </c>
-      <c r="B112" s="13">
+      <c r="B112" s="10">
         <v>45649</v>
       </c>
       <c r="C112" s="4">
@@ -22941,10 +23025,10 @@
       <c r="S112" s="1"/>
     </row>
     <row r="113" spans="1:19">
-      <c r="A113" s="13">
+      <c r="A113" s="10">
         <v>45656</v>
       </c>
-      <c r="B113" s="13">
+      <c r="B113" s="10">
         <v>45656</v>
       </c>
       <c r="C113" s="4">
@@ -22998,10 +23082,10 @@
       <c r="S113" s="1"/>
     </row>
     <row r="114" spans="1:19">
-      <c r="A114" s="13">
+      <c r="A114" s="10">
         <v>45663</v>
       </c>
-      <c r="B114" s="13">
+      <c r="B114" s="10">
         <v>45663</v>
       </c>
       <c r="C114" s="4">
@@ -23055,10 +23139,10 @@
       <c r="S114" s="1"/>
     </row>
     <row r="115" spans="1:19">
-      <c r="A115" s="13">
+      <c r="A115" s="10">
         <v>45670</v>
       </c>
-      <c r="B115" s="13">
+      <c r="B115" s="10">
         <v>45670</v>
       </c>
       <c r="C115" s="4">
@@ -23112,10 +23196,10 @@
       <c r="S115" s="1"/>
     </row>
     <row r="116" spans="1:19">
-      <c r="A116" s="13">
+      <c r="A116" s="10">
         <v>45677</v>
       </c>
-      <c r="B116" s="13">
+      <c r="B116" s="10">
         <v>45677</v>
       </c>
       <c r="C116" s="4">
@@ -23169,10 +23253,10 @@
       <c r="S116" s="1"/>
     </row>
     <row r="117" spans="1:19">
-      <c r="A117" s="13">
+      <c r="A117" s="10">
         <v>45691</v>
       </c>
-      <c r="B117" s="13">
+      <c r="B117" s="10">
         <v>45691</v>
       </c>
       <c r="C117" s="4">
@@ -23226,10 +23310,10 @@
       <c r="S117" s="1"/>
     </row>
     <row r="118" spans="1:19">
-      <c r="A118" s="13">
+      <c r="A118" s="10">
         <v>45698</v>
       </c>
-      <c r="B118" s="13">
+      <c r="B118" s="10">
         <v>45698</v>
       </c>
       <c r="C118" s="4">
@@ -23283,10 +23367,10 @@
       <c r="S118" s="1"/>
     </row>
     <row r="119" spans="1:19">
-      <c r="A119" s="13">
+      <c r="A119" s="10">
         <v>45705</v>
       </c>
-      <c r="B119" s="13">
+      <c r="B119" s="10">
         <v>45705</v>
       </c>
       <c r="C119" s="4">
@@ -23340,10 +23424,10 @@
       <c r="S119" s="1"/>
     </row>
     <row r="120" spans="1:19">
-      <c r="A120" s="13">
+      <c r="A120" s="10">
         <v>45712</v>
       </c>
-      <c r="B120" s="13">
+      <c r="B120" s="10">
         <v>45712</v>
       </c>
       <c r="C120" s="4">
@@ -23397,10 +23481,10 @@
       <c r="S120" s="1"/>
     </row>
     <row r="121" spans="1:19">
-      <c r="A121" s="13">
+      <c r="A121" s="10">
         <v>45720</v>
       </c>
-      <c r="B121" s="13">
+      <c r="B121" s="10">
         <v>45720</v>
       </c>
       <c r="C121" s="4">
@@ -23454,10 +23538,10 @@
       <c r="S121" s="1"/>
     </row>
     <row r="122" spans="1:19">
-      <c r="A122" s="13">
+      <c r="A122" s="10">
         <v>45726</v>
       </c>
-      <c r="B122" s="13">
+      <c r="B122" s="10">
         <v>45726</v>
       </c>
       <c r="C122" s="4">
@@ -23511,10 +23595,10 @@
       <c r="S122" s="1"/>
     </row>
     <row r="123" spans="1:19">
-      <c r="A123" s="13">
+      <c r="A123" s="10">
         <v>45733</v>
       </c>
-      <c r="B123" s="13">
+      <c r="B123" s="10">
         <v>45733</v>
       </c>
       <c r="C123" s="4">
@@ -23568,10 +23652,10 @@
       <c r="S123" s="1"/>
     </row>
     <row r="124" spans="1:19">
-      <c r="A124" s="13">
+      <c r="A124" s="10">
         <v>45740</v>
       </c>
-      <c r="B124" s="13">
+      <c r="B124" s="10">
         <v>45740</v>
       </c>
       <c r="C124" s="4">
@@ -23625,10 +23709,10 @@
       <c r="S124" s="1"/>
     </row>
     <row r="125" spans="1:19">
-      <c r="A125" s="13">
+      <c r="A125" s="10">
         <v>45747</v>
       </c>
-      <c r="B125" s="13">
+      <c r="B125" s="10">
         <v>45747</v>
       </c>
       <c r="C125" s="4">
@@ -23682,10 +23766,10 @@
       <c r="S125" s="1"/>
     </row>
     <row r="126" spans="1:19">
-      <c r="A126" s="13">
+      <c r="A126" s="10">
         <v>45754</v>
       </c>
-      <c r="B126" s="13">
+      <c r="B126" s="10">
         <v>45754</v>
       </c>
       <c r="C126" s="4">
@@ -23739,10 +23823,10 @@
       <c r="S126" s="1"/>
     </row>
     <row r="127" spans="1:19">
-      <c r="A127" s="13">
+      <c r="A127" s="10">
         <v>45761</v>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="10">
         <v>45761</v>
       </c>
       <c r="C127" s="4">
@@ -23796,10 +23880,10 @@
       <c r="S127" s="1"/>
     </row>
     <row r="128" spans="1:19">
-      <c r="A128" s="13">
+      <c r="A128" s="10">
         <v>45768</v>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="10">
         <v>45768</v>
       </c>
       <c r="C128" s="4">
@@ -23853,10 +23937,10 @@
       <c r="S128" s="1"/>
     </row>
     <row r="129" spans="1:19">
-      <c r="A129" s="13">
+      <c r="A129" s="10">
         <v>45775</v>
       </c>
-      <c r="B129" s="13">
+      <c r="B129" s="10">
         <v>45775</v>
       </c>
       <c r="C129" s="4">
@@ -23910,10 +23994,10 @@
       <c r="S129" s="1"/>
     </row>
     <row r="130" spans="1:19">
-      <c r="A130" s="13">
+      <c r="A130" s="10">
         <v>45789</v>
       </c>
-      <c r="B130" s="13">
+      <c r="B130" s="10">
         <v>45789</v>
       </c>
       <c r="C130" s="4">
@@ -23967,10 +24051,10 @@
       <c r="S130" s="1"/>
     </row>
     <row r="131" spans="1:19">
-      <c r="A131" s="13">
+      <c r="A131" s="10">
         <v>45796</v>
       </c>
-      <c r="B131" s="13">
+      <c r="B131" s="10">
         <v>45796</v>
       </c>
       <c r="C131" s="4">
@@ -24024,10 +24108,10 @@
       <c r="S131" s="1"/>
     </row>
     <row r="132" spans="1:19">
-      <c r="A132" s="13">
+      <c r="A132" s="10">
         <v>45803</v>
       </c>
-      <c r="B132" s="13">
+      <c r="B132" s="10">
         <v>45803</v>
       </c>
       <c r="C132" s="4">
@@ -24081,10 +24165,10 @@
       <c r="S132" s="1"/>
     </row>
     <row r="133" spans="1:19">
-      <c r="A133" s="13">
+      <c r="A133" s="10">
         <v>45810</v>
       </c>
-      <c r="B133" s="13">
+      <c r="B133" s="10">
         <v>45810</v>
       </c>
       <c r="C133" s="4">
@@ -24138,10 +24222,10 @@
       <c r="S133" s="1"/>
     </row>
     <row r="134" spans="1:19">
-      <c r="A134" s="13">
+      <c r="A134" s="10">
         <v>45817</v>
       </c>
-      <c r="B134" s="13">
+      <c r="B134" s="10">
         <v>45817</v>
       </c>
       <c r="C134" s="4">
@@ -24195,10 +24279,10 @@
       <c r="S134" s="1"/>
     </row>
     <row r="135" spans="1:19">
-      <c r="A135" s="13">
+      <c r="A135" s="10">
         <v>45824</v>
       </c>
-      <c r="B135" s="13">
+      <c r="B135" s="10">
         <v>45824</v>
       </c>
       <c r="C135" s="4">
@@ -24252,10 +24336,10 @@
       <c r="S135" s="1"/>
     </row>
     <row r="136" spans="1:19">
-      <c r="A136" s="13">
+      <c r="A136" s="10">
         <v>45831</v>
       </c>
-      <c r="B136" s="13">
+      <c r="B136" s="10">
         <v>45831</v>
       </c>
       <c r="C136" s="4">
@@ -24309,10 +24393,10 @@
       <c r="S136" s="1"/>
     </row>
     <row r="137" spans="1:19">
-      <c r="A137" s="13">
+      <c r="A137" s="10">
         <v>45838</v>
       </c>
-      <c r="B137" s="13">
+      <c r="B137" s="10">
         <v>45838</v>
       </c>
       <c r="C137" s="4">
@@ -24366,10 +24450,10 @@
       <c r="S137" s="1"/>
     </row>
     <row r="138" spans="1:19">
-      <c r="A138" s="13">
+      <c r="A138" s="10">
         <v>45845</v>
       </c>
-      <c r="B138" s="13">
+      <c r="B138" s="10">
         <v>45845</v>
       </c>
       <c r="C138" s="4">
@@ -24423,10 +24507,10 @@
       <c r="S138" s="1"/>
     </row>
     <row r="139" spans="1:19">
-      <c r="A139" s="13">
+      <c r="A139" s="10">
         <v>45852</v>
       </c>
-      <c r="B139" s="13">
+      <c r="B139" s="10">
         <v>45852</v>
       </c>
       <c r="C139" s="4">
@@ -24480,10 +24564,10 @@
       <c r="S139" s="1"/>
     </row>
     <row r="140" spans="1:19">
-      <c r="A140" s="13">
+      <c r="A140" s="10">
         <v>45859</v>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="10">
         <v>45859</v>
       </c>
       <c r="C140" s="4">
@@ -24537,10 +24621,10 @@
       <c r="S140" s="1"/>
     </row>
     <row r="141" spans="1:19">
-      <c r="A141" s="13">
+      <c r="A141" s="10">
         <v>45866</v>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="10">
         <v>45866</v>
       </c>
       <c r="C141" s="4">
@@ -24594,10 +24678,10 @@
       <c r="S141" s="1"/>
     </row>
     <row r="142" spans="1:19">
-      <c r="A142" s="13">
+      <c r="A142" s="10">
         <v>45873</v>
       </c>
-      <c r="B142" s="13">
+      <c r="B142" s="10">
         <v>45873</v>
       </c>
       <c r="C142" s="4">
@@ -24651,10 +24735,10 @@
       <c r="S142" s="1"/>
     </row>
     <row r="143" spans="1:19">
-      <c r="A143" s="13">
+      <c r="A143" s="10">
         <v>45880</v>
       </c>
-      <c r="B143" s="13">
+      <c r="B143" s="10">
         <v>45880</v>
       </c>
       <c r="C143" s="4">
@@ -24708,10 +24792,10 @@
       <c r="S143" s="1"/>
     </row>
     <row r="144" spans="1:19">
-      <c r="A144" s="13">
+      <c r="A144" s="10">
         <v>45887</v>
       </c>
-      <c r="B144" s="13">
+      <c r="B144" s="10">
         <v>45887</v>
       </c>
       <c r="C144" s="4">
@@ -24765,10 +24849,10 @@
       <c r="S144" s="1"/>
     </row>
     <row r="145" spans="1:19">
-      <c r="A145" s="13">
+      <c r="A145" s="10">
         <v>45894</v>
       </c>
-      <c r="B145" s="13">
+      <c r="B145" s="10">
         <v>45894</v>
       </c>
       <c r="C145" s="4">
@@ -24822,10 +24906,10 @@
       <c r="S145" s="1"/>
     </row>
     <row r="146" spans="1:19">
-      <c r="A146" s="13">
+      <c r="A146" s="10">
         <v>45901</v>
       </c>
-      <c r="B146" s="13">
+      <c r="B146" s="10">
         <v>45901</v>
       </c>
       <c r="C146" s="4">
@@ -24879,10 +24963,10 @@
       <c r="S146" s="1"/>
     </row>
     <row r="147" spans="1:19">
-      <c r="A147" s="13">
+      <c r="A147" s="10">
         <v>45908</v>
       </c>
-      <c r="B147" s="13">
+      <c r="B147" s="10">
         <v>45908</v>
       </c>
       <c r="C147" s="4">
@@ -24936,10 +25020,10 @@
       <c r="S147" s="1"/>
     </row>
     <row r="148" spans="1:19">
-      <c r="A148" s="13">
+      <c r="A148" s="10">
         <v>45915</v>
       </c>
-      <c r="B148" s="13">
+      <c r="B148" s="10">
         <v>45915</v>
       </c>
       <c r="C148" s="4">
@@ -24993,10 +25077,10 @@
       <c r="S148" s="1"/>
     </row>
     <row r="149" spans="1:19">
-      <c r="A149" s="13">
+      <c r="A149" s="10">
         <v>45922</v>
       </c>
-      <c r="B149" s="13">
+      <c r="B149" s="10">
         <v>45922</v>
       </c>
       <c r="C149" s="4">
@@ -25050,10 +25134,10 @@
       <c r="S149" s="1"/>
     </row>
     <row r="150" spans="1:19">
-      <c r="A150" s="13">
+      <c r="A150" s="10">
         <v>45929</v>
       </c>
-      <c r="B150" s="13">
+      <c r="B150" s="10">
         <v>45929</v>
       </c>
       <c r="C150" s="4">
@@ -25107,10 +25191,10 @@
       <c r="S150" s="1"/>
     </row>
     <row r="151" spans="1:19">
-      <c r="A151" s="13">
+      <c r="A151" s="10">
         <v>45950</v>
       </c>
-      <c r="B151" s="13">
+      <c r="B151" s="10">
         <v>45950</v>
       </c>
       <c r="C151" s="4">
@@ -25164,10 +25248,10 @@
       <c r="S151" s="1"/>
     </row>
     <row r="152" spans="1:19">
-      <c r="A152" s="13">
+      <c r="A152" s="10">
         <v>45957</v>
       </c>
-      <c r="B152" s="13">
+      <c r="B152" s="10">
         <v>45957</v>
       </c>
       <c r="C152" s="4">
@@ -25221,10 +25305,10 @@
       <c r="S152" s="1"/>
     </row>
     <row r="153" spans="1:19">
-      <c r="A153" s="13">
+      <c r="A153" s="10">
         <v>45964</v>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="10">
         <v>45964</v>
       </c>
       <c r="C153" s="4">
@@ -25278,10 +25362,10 @@
       <c r="S153" s="1"/>
     </row>
     <row r="154" spans="1:19">
-      <c r="A154" s="13">
+      <c r="A154" s="10">
         <v>45971</v>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="10">
         <v>45971</v>
       </c>
       <c r="C154" s="4">
@@ -25335,10 +25419,10 @@
       <c r="S154" s="1"/>
     </row>
     <row r="155" spans="1:19">
-      <c r="A155" s="13">
+      <c r="A155" s="10">
         <v>45978</v>
       </c>
-      <c r="B155" s="13">
+      <c r="B155" s="10">
         <v>45978</v>
       </c>
       <c r="C155" s="4">
@@ -25392,10 +25476,10 @@
       <c r="S155" s="1"/>
     </row>
     <row r="156" spans="1:19">
-      <c r="A156" s="13">
+      <c r="A156" s="10">
         <v>45985</v>
       </c>
-      <c r="B156" s="13">
+      <c r="B156" s="10">
         <v>45985</v>
       </c>
       <c r="C156" s="4">
@@ -25449,10 +25533,10 @@
       <c r="S156" s="1"/>
     </row>
     <row r="157" spans="1:19">
-      <c r="A157" s="13">
+      <c r="A157" s="10">
         <v>45992</v>
       </c>
-      <c r="B157" s="13">
+      <c r="B157" s="10">
         <v>45992</v>
       </c>
       <c r="C157" s="4">
@@ -25506,10 +25590,10 @@
       <c r="S157" s="1"/>
     </row>
     <row r="158" spans="1:19">
-      <c r="A158" s="13">
+      <c r="A158" s="10">
         <v>45999</v>
       </c>
-      <c r="B158" s="13">
+      <c r="B158" s="10">
         <v>45999</v>
       </c>
       <c r="C158" s="4">
@@ -25563,10 +25647,10 @@
       <c r="S158" s="1"/>
     </row>
     <row r="159" spans="1:19">
-      <c r="A159" s="13">
+      <c r="A159" s="10">
         <v>46006</v>
       </c>
-      <c r="B159" s="13">
+      <c r="B159" s="10">
         <v>46006</v>
       </c>
       <c r="C159" s="4">
@@ -25620,10 +25704,10 @@
       <c r="S159" s="1"/>
     </row>
     <row r="160" spans="1:19">
-      <c r="A160" s="13">
+      <c r="A160" s="10">
         <v>46013</v>
       </c>
-      <c r="B160" s="13">
+      <c r="B160" s="10">
         <v>46013</v>
       </c>
       <c r="C160" s="4">
@@ -25677,10 +25761,10 @@
       <c r="S160" s="1"/>
     </row>
     <row r="161" spans="1:19">
-      <c r="A161" s="13">
+      <c r="A161" s="10">
         <v>46020</v>
       </c>
-      <c r="B161" s="13">
+      <c r="B161" s="10">
         <v>46020</v>
       </c>
       <c r="C161" s="4">
@@ -25734,10 +25818,10 @@
       <c r="S161" s="1"/>
     </row>
     <row r="162" spans="1:19">
-      <c r="A162" s="13">
+      <c r="A162" s="10">
         <v>46034</v>
       </c>
-      <c r="B162" s="13">
+      <c r="B162" s="10">
         <v>46034</v>
       </c>
       <c r="C162" s="4">
@@ -25791,10 +25875,10 @@
       <c r="S162" s="1"/>
     </row>
     <row r="163" spans="1:19">
-      <c r="A163" s="13">
+      <c r="A163" s="10">
         <v>46041</v>
       </c>
-      <c r="B163" s="13">
+      <c r="B163" s="10">
         <v>46041</v>
       </c>
       <c r="C163" s="4">
@@ -25848,10 +25932,10 @@
       <c r="S163" s="1"/>
     </row>
     <row r="164" spans="1:19">
-      <c r="A164" s="13">
+      <c r="A164" s="10">
         <v>46048</v>
       </c>
-      <c r="B164" s="13">
+      <c r="B164" s="10">
         <v>46048</v>
       </c>
       <c r="C164" s="4">
@@ -25905,10 +25989,10 @@
       <c r="S164" s="1"/>
     </row>
     <row r="165" spans="1:19">
-      <c r="A165" s="13">
+      <c r="A165" s="10">
         <v>46055</v>
       </c>
-      <c r="B165" s="13">
+      <c r="B165" s="10">
         <v>46055</v>
       </c>
       <c r="C165" s="4">
@@ -25962,10 +26046,10 @@
       <c r="S165" s="1"/>
     </row>
     <row r="166" spans="1:19">
-      <c r="A166" s="13">
+      <c r="A166" s="10">
         <v>46062</v>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="10">
         <v>46062</v>
       </c>
       <c r="C166" s="4">
@@ -26019,10 +26103,10 @@
       <c r="S166" s="1"/>
     </row>
     <row r="167" spans="1:19">
-      <c r="A167" s="13">
+      <c r="A167" s="10">
         <v>46076</v>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="10">
         <v>46076</v>
       </c>
       <c r="C167" s="4">
@@ -26075,10 +26159,10 @@
       </c>
     </row>
     <row r="168" spans="1:19">
-      <c r="A168" s="13">
+      <c r="A168" s="10">
         <v>46084</v>
       </c>
-      <c r="B168" s="13">
+      <c r="B168" s="10">
         <v>46084</v>
       </c>
       <c r="C168" s="4">
@@ -26131,10 +26215,10 @@
       </c>
     </row>
     <row r="169" spans="1:19">
-      <c r="A169" s="13">
+      <c r="A169" s="10">
         <v>46090</v>
       </c>
-      <c r="B169" s="13">
+      <c r="B169" s="10">
         <v>46090</v>
       </c>
       <c r="C169" s="4">
@@ -26187,10 +26271,10 @@
       </c>
     </row>
     <row r="170" spans="1:19">
-      <c r="A170" s="13">
+      <c r="A170" s="10">
         <v>46097</v>
       </c>
-      <c r="B170" s="13">
+      <c r="B170" s="10">
         <v>46097</v>
       </c>
       <c r="C170" s="4">
@@ -26243,10 +26327,10 @@
       </c>
     </row>
     <row r="171" spans="1:19">
-      <c r="A171" s="13">
+      <c r="A171" s="10">
         <v>46104</v>
       </c>
-      <c r="B171" s="13">
+      <c r="B171" s="10">
         <v>46104</v>
       </c>
       <c r="C171" s="4">
@@ -26299,10 +26383,10 @@
       </c>
     </row>
     <row r="172" spans="1:19">
-      <c r="A172" s="13">
+      <c r="A172" s="10">
         <v>46111</v>
       </c>
-      <c r="B172" s="13">
+      <c r="B172" s="10">
         <v>46111</v>
       </c>
       <c r="C172" s="4">
@@ -26352,6 +26436,62 @@
       </c>
       <c r="R172" s="7">
         <v>1024</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19">
+      <c r="A173" s="10">
+        <v>46118</v>
+      </c>
+      <c r="B173" s="10">
+        <v>46118</v>
+      </c>
+      <c r="C173" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E173" s="7">
+        <v>2178</v>
+      </c>
+      <c r="F173" s="7">
+        <v>2467</v>
+      </c>
+      <c r="G173" s="7">
+        <v>3406</v>
+      </c>
+      <c r="H173" s="7">
+        <v>2646</v>
+      </c>
+      <c r="I173" s="7">
+        <v>3730</v>
+      </c>
+      <c r="J173" s="7">
+        <v>6211</v>
+      </c>
+      <c r="K173" s="7">
+        <v>1509</v>
+      </c>
+      <c r="L173" s="7">
+        <v>3148</v>
+      </c>
+      <c r="M173" s="7">
+        <v>3089</v>
+      </c>
+      <c r="N173" s="7">
+        <v>2984</v>
+      </c>
+      <c r="O173" s="7">
+        <v>4068</v>
+      </c>
+      <c r="P173" s="7">
+        <v>59</v>
+      </c>
+      <c r="Q173" s="7">
+        <v>246</v>
+      </c>
+      <c r="R173" s="7">
+        <v>1070</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4197DD-DEA5-42E8-AD29-ABD0DEF514E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91377AD2-8D05-47DD-86B8-494CCBB63E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -879,6 +879,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1403,6 +1406,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>2186</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2193</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1965,6 +1971,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2489,6 +2498,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>2616</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2725</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3051,6 +3063,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3575,6 +3590,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>3600</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3728</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4137,6 +4155,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4661,6 +4682,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>2534</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5223,6 +5247,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5747,6 +5774,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>3574</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3480</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6309,6 +6339,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6833,6 +6866,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>6249</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>6085</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7397,6 +7433,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7921,6 +7960,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>1502</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8485,6 +8527,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9009,6 +9054,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>3068</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9573,6 +9621,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10097,6 +10148,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>2959</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10661,6 +10715,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11185,6 +11242,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>2874</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2925</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11749,6 +11809,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12273,6 +12336,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>4042</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12853,6 +12919,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13377,6 +13446,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13942,6 +14014,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14465,6 +14540,9 @@
                   <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="171">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="172">
                   <c:v>245</c:v>
                 </c:pt>
               </c:numCache>
@@ -15031,6 +15109,9 @@
                 <c:pt idx="171">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15555,6 +15636,9 @@
                 </c:pt>
                 <c:pt idx="171">
                   <c:v>1085</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16722,7 +16806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S174"/>
+  <dimension ref="A1:S175"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
@@ -26632,6 +26716,62 @@
       </c>
       <c r="R174" s="7">
         <v>1085</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A175" s="10">
+        <v>46132</v>
+      </c>
+      <c r="B175" s="10">
+        <v>46132</v>
+      </c>
+      <c r="C175" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E175" s="7">
+        <v>2193</v>
+      </c>
+      <c r="F175" s="7">
+        <v>2725</v>
+      </c>
+      <c r="G175" s="7">
+        <v>3728</v>
+      </c>
+      <c r="H175" s="7">
+        <v>2401</v>
+      </c>
+      <c r="I175" s="7">
+        <v>3480</v>
+      </c>
+      <c r="J175" s="7">
+        <v>6085</v>
+      </c>
+      <c r="K175" s="7">
+        <v>1618</v>
+      </c>
+      <c r="L175" s="7">
+        <v>3000</v>
+      </c>
+      <c r="M175" s="7">
+        <v>2849</v>
+      </c>
+      <c r="N175" s="7">
+        <v>2925</v>
+      </c>
+      <c r="O175" s="7">
+        <v>4158</v>
+      </c>
+      <c r="P175" s="7">
+        <v>56</v>
+      </c>
+      <c r="Q175" s="7">
+        <v>245</v>
+      </c>
+      <c r="R175" s="7">
+        <v>1095</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91377AD2-8D05-47DD-86B8-494CCBB63E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A7A7BF-7EDB-4568-9B7D-D7F75A1EE6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -882,6 +882,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1409,6 +1412,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>2193</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1974,6 +1980,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2501,6 +2510,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>2725</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2752</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3066,6 +3078,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3593,6 +3608,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>3728</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4158,6 +4176,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4685,6 +4706,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>2401</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2377</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5250,6 +5274,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5777,6 +5804,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>3480</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3460</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6342,6 +6372,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6869,6 +6902,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>6085</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>6147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7436,6 +7472,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7963,6 +8002,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>1618</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1691</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8530,6 +8572,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9057,6 +9102,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2854</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9624,6 +9672,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10151,6 +10202,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>2849</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10718,6 +10772,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11245,6 +11302,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>2925</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2911</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11812,6 +11872,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12339,6 +12402,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>4158</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12922,6 +12988,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13448,6 +13517,9 @@
                   <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="172">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
@@ -14017,6 +14089,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14543,6 +14618,9 @@
                   <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="172">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>245</c:v>
                 </c:pt>
               </c:numCache>
@@ -15112,6 +15190,9 @@
                 <c:pt idx="172">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="173">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15639,6 +15720,9 @@
                 </c:pt>
                 <c:pt idx="172">
                   <c:v>1095</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16806,7 +16890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S175"/>
+  <dimension ref="A1:S176"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
@@ -26772,6 +26856,62 @@
       </c>
       <c r="R175" s="7">
         <v>1095</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A176" s="10">
+        <v>46139</v>
+      </c>
+      <c r="B176" s="10">
+        <v>46139</v>
+      </c>
+      <c r="C176" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E176" s="7">
+        <v>2192</v>
+      </c>
+      <c r="F176" s="7">
+        <v>2752</v>
+      </c>
+      <c r="G176" s="7">
+        <v>3743</v>
+      </c>
+      <c r="H176" s="7">
+        <v>2377</v>
+      </c>
+      <c r="I176" s="7">
+        <v>3460</v>
+      </c>
+      <c r="J176" s="7">
+        <v>6147</v>
+      </c>
+      <c r="K176" s="7">
+        <v>1691</v>
+      </c>
+      <c r="L176" s="7">
+        <v>2854</v>
+      </c>
+      <c r="M176" s="7">
+        <v>2785</v>
+      </c>
+      <c r="N176" s="7">
+        <v>2911</v>
+      </c>
+      <c r="O176" s="7">
+        <v>4149</v>
+      </c>
+      <c r="P176" s="7">
+        <v>56</v>
+      </c>
+      <c r="Q176" s="7">
+        <v>245</v>
+      </c>
+      <c r="R176" s="7">
+        <v>1097</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168AFC5F-D800-4592-9BB9-0EF134C458C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478CE8CD-7BD9-4E57-BDED-083FDC00AE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -22,12 +22,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -163,7 +172,6 @@
   </si>
   <si>
     <t>https://www.kobc.or.kr/ebz/shippinginfo/kcci/gridList.do?mId=0304000000&amp;token=1771488048621</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -171,9 +179,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -259,16 +267,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -277,13 +285,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -888,6 +896,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -895,7 +906,7 @@
             <c:numRef>
               <c:f>KCCI!$E$3:$E$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>2892</c:v>
@@ -1421,6 +1432,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>2194</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>2361</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1992,6 +2006,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1999,7 +2016,7 @@
             <c:numRef>
               <c:f>KCCI!$F$3:$F$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1934</c:v>
@@ -2525,6 +2542,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>2753</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3096,6 +3116,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3103,7 +3126,7 @@
             <c:numRef>
               <c:f>KCCI!$G$3:$G$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5383</c:v>
@@ -3629,6 +3652,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>3787</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4103</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4200,6 +4226,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4207,7 +4236,7 @@
             <c:numRef>
               <c:f>KCCI!$H$3:$H$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4016</c:v>
@@ -4733,6 +4762,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>2353</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>2679</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5304,6 +5336,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5311,7 +5346,7 @@
             <c:numRef>
               <c:f>KCCI!$I$3:$I$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4475</c:v>
@@ -5837,6 +5872,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>3415</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3866</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6408,6 +6446,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6415,7 +6456,7 @@
             <c:numRef>
               <c:f>KCCI!$J$3:$J$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3359</c:v>
@@ -6941,6 +6982,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>5939</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5934</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7514,6 +7558,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7521,7 +7568,7 @@
             <c:numRef>
               <c:f>KCCI!$K$3:$K$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4166</c:v>
@@ -8047,6 +8094,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>1729</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1864</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8620,6 +8670,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8627,7 +8680,7 @@
             <c:numRef>
               <c:f>KCCI!$L$3:$L$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5075</c:v>
@@ -9153,6 +9206,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>3007</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3484</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9726,6 +9782,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9733,7 +9792,7 @@
             <c:numRef>
               <c:f>KCCI!$M$3:$M$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3854</c:v>
@@ -10259,6 +10318,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>2742</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3054</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10832,6 +10894,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10839,7 +10904,7 @@
             <c:numRef>
               <c:f>KCCI!$N$3:$N$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6459</c:v>
@@ -11365,6 +11430,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>3177</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11938,6 +12006,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11945,7 +12016,7 @@
             <c:numRef>
               <c:f>KCCI!$O$3:$O$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6028</c:v>
@@ -12471,6 +12542,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>4251</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13060,6 +13134,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13067,7 +13144,7 @@
             <c:numRef>
               <c:f>KCCI!$P$3:$P$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>295</c:v>
@@ -13592,6 +13669,9 @@
                   <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="174">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="175">
                   <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
@@ -14167,6 +14247,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14174,7 +14257,7 @@
             <c:numRef>
               <c:f>KCCI!$Q$3:$Q$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>881</c:v>
@@ -14700,6 +14783,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15274,6 +15360,9 @@
                 <c:pt idx="174">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15281,7 +15370,7 @@
             <c:numRef>
               <c:f>KCCI!$R$3:$R$11165</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1708</c:v>
@@ -15807,6 +15896,9 @@
                 </c:pt>
                 <c:pt idx="174">
                   <c:v>1077</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15906,7 +15998,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -15948,7 +16040,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -16974,7 +17066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S177"/>
+  <dimension ref="A1:S178"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
@@ -27052,6 +27144,62 @@
       </c>
       <c r="R177" s="7">
         <v>1077</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A178" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B178" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C178" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E178" s="7">
+        <v>2361</v>
+      </c>
+      <c r="F178" s="7">
+        <v>3011</v>
+      </c>
+      <c r="G178" s="7">
+        <v>4103</v>
+      </c>
+      <c r="H178" s="7">
+        <v>2679</v>
+      </c>
+      <c r="I178" s="7">
+        <v>3866</v>
+      </c>
+      <c r="J178" s="7">
+        <v>5934</v>
+      </c>
+      <c r="K178" s="7">
+        <v>1864</v>
+      </c>
+      <c r="L178" s="7">
+        <v>3484</v>
+      </c>
+      <c r="M178" s="7">
+        <v>3054</v>
+      </c>
+      <c r="N178" s="7">
+        <v>3035</v>
+      </c>
+      <c r="O178" s="7">
+        <v>4250</v>
+      </c>
+      <c r="P178" s="7">
+        <v>56</v>
+      </c>
+      <c r="Q178" s="7">
+        <v>238</v>
+      </c>
+      <c r="R178" s="7">
+        <v>1075</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61F9D6-EE98-4B02-8A86-9BED797F2242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2A7AB9-78E8-4C80-8A8A-AFAB039C44ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -902,6 +902,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1441,6 +1444,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>2478</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>2675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2018,6 +2024,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2557,6 +2566,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>3135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3134,6 +3146,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3673,6 +3688,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>4257</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4250,6 +4268,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4789,6 +4810,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>2838</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3120</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5366,6 +5390,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5905,6 +5932,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>4133</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6482,6 +6512,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7021,6 +7054,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>5991</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>6003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7600,6 +7636,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8139,6 +8178,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>2189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8718,6 +8760,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9257,6 +9302,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>3967</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4676</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9836,6 +9884,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10375,6 +10426,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>3340</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3847</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10954,6 +11008,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11493,6 +11550,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>3060</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12072,6 +12132,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12611,6 +12674,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>4326</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4419</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13206,6 +13272,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13744,6 +13813,9 @@
                   <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="176">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="177">
                   <c:v>52</c:v>
                 </c:pt>
               </c:numCache>
@@ -14325,6 +14397,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14863,6 +14938,9 @@
                   <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="176">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="177">
                   <c:v>238</c:v>
                 </c:pt>
               </c:numCache>
@@ -15444,6 +15522,9 @@
                 <c:pt idx="176">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="177">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15983,6 +16064,9 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>1075</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17150,7 +17234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S179"/>
+  <dimension ref="A1:S180"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
@@ -27340,6 +27424,62 @@
       </c>
       <c r="R179" s="7">
         <v>1075</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A180" s="10">
+        <v>46174</v>
+      </c>
+      <c r="B180" s="10">
+        <v>46174</v>
+      </c>
+      <c r="C180" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E180" s="7">
+        <v>2675</v>
+      </c>
+      <c r="F180" s="7">
+        <v>3456</v>
+      </c>
+      <c r="G180" s="7">
+        <v>4572</v>
+      </c>
+      <c r="H180" s="7">
+        <v>3120</v>
+      </c>
+      <c r="I180" s="7">
+        <v>4344</v>
+      </c>
+      <c r="J180" s="7">
+        <v>6003</v>
+      </c>
+      <c r="K180" s="7">
+        <v>2189</v>
+      </c>
+      <c r="L180" s="7">
+        <v>4676</v>
+      </c>
+      <c r="M180" s="7">
+        <v>3847</v>
+      </c>
+      <c r="N180" s="7">
+        <v>3181</v>
+      </c>
+      <c r="O180" s="7">
+        <v>4419</v>
+      </c>
+      <c r="P180" s="7">
+        <v>52</v>
+      </c>
+      <c r="Q180" s="7">
+        <v>238</v>
+      </c>
+      <c r="R180" s="7">
+        <v>1142</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2A7AB9-78E8-4C80-8A8A-AFAB039C44ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F72471-46DE-4C85-B55C-7239A580F335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="KCCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -183,7 +183,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -299,9 +299,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -319,7 +319,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -905,6 +905,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1447,6 +1450,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>2675</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3042</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2027,6 +2033,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2569,6 +2578,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>3456</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3149,6 +3161,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3691,6 +3706,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>4572</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4271,6 +4289,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4813,6 +4834,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>3120</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3679</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5393,6 +5417,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5935,6 +5962,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>4344</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4877</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6515,6 +6545,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7057,6 +7090,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>6003</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>6011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7639,6 +7675,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8181,6 +8220,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>2189</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>2423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8763,6 +8805,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9305,6 +9350,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>4676</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9887,6 +9935,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10429,6 +10480,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>3847</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4321</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11011,6 +11065,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11553,6 +11610,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>3181</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3274</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12135,6 +12195,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12677,6 +12740,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>4419</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4679</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13275,6 +13341,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13817,6 +13886,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>51</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14400,6 +14472,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14942,6 +15017,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15525,6 +15603,9 @@
                 <c:pt idx="177">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16067,6 +16148,9 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>1142</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16938,9 +17022,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -16978,7 +17062,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -17084,7 +17168,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -17226,7 +17310,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -17234,19 +17318,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S180"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S181"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" style="3" customWidth="1"/>
-    <col min="5" max="18" width="12.77734375" style="7" customWidth="1"/>
-    <col min="19" max="19" width="11.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.21875" style="2"/>
+    <col min="1" max="1" width="13.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" style="3" customWidth="1"/>
+    <col min="5" max="18" width="12.81640625" style="7" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -17302,7 +17386,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
@@ -17350,7 +17434,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19">
       <c r="A3" s="10">
         <v>44872</v>
       </c>
@@ -17407,7 +17491,7 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19">
       <c r="A4" s="10">
         <v>44879</v>
       </c>
@@ -17464,7 +17548,7 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19">
       <c r="A5" s="10">
         <v>44886</v>
       </c>
@@ -17521,7 +17605,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19">
       <c r="A6" s="10">
         <v>44893</v>
       </c>
@@ -17578,7 +17662,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19">
       <c r="A7" s="10">
         <v>44900</v>
       </c>
@@ -17635,7 +17719,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19">
       <c r="A8" s="10">
         <v>44907</v>
       </c>
@@ -17692,7 +17776,7 @@
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19">
       <c r="A9" s="10">
         <v>44914</v>
       </c>
@@ -17749,7 +17833,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19">
       <c r="A10" s="10">
         <v>44921</v>
       </c>
@@ -17806,7 +17890,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19">
       <c r="A11" s="10">
         <v>44928</v>
       </c>
@@ -17863,7 +17947,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19">
       <c r="A12" s="10">
         <v>44935</v>
       </c>
@@ -17920,7 +18004,7 @@
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19">
       <c r="A13" s="10">
         <v>44942</v>
       </c>
@@ -17977,7 +18061,7 @@
       </c>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19">
       <c r="A14" s="10">
         <v>44951</v>
       </c>
@@ -18034,7 +18118,7 @@
       </c>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19">
       <c r="A15" s="10">
         <v>44956</v>
       </c>
@@ -18091,7 +18175,7 @@
       </c>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19">
       <c r="A16" s="10">
         <v>44963</v>
       </c>
@@ -18148,7 +18232,7 @@
       </c>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19">
       <c r="A17" s="10">
         <v>44970</v>
       </c>
@@ -18205,7 +18289,7 @@
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19">
       <c r="A18" s="10">
         <v>44977</v>
       </c>
@@ -18262,7 +18346,7 @@
       </c>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19">
       <c r="A19" s="10">
         <v>44984</v>
       </c>
@@ -18319,7 +18403,7 @@
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19">
       <c r="A20" s="10">
         <v>44991</v>
       </c>
@@ -18376,7 +18460,7 @@
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19">
       <c r="A21" s="10">
         <v>44998</v>
       </c>
@@ -18433,7 +18517,7 @@
       </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19">
       <c r="A22" s="10">
         <v>45005</v>
       </c>
@@ -18490,7 +18574,7 @@
       </c>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19">
       <c r="A23" s="10">
         <v>45012</v>
       </c>
@@ -18547,7 +18631,7 @@
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19">
       <c r="A24" s="10">
         <v>45019</v>
       </c>
@@ -18604,7 +18688,7 @@
       </c>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19">
       <c r="A25" s="10">
         <v>45026</v>
       </c>
@@ -18661,7 +18745,7 @@
       </c>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19">
       <c r="A26" s="10">
         <v>45033</v>
       </c>
@@ -18718,7 +18802,7 @@
       </c>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19">
       <c r="A27" s="10">
         <v>45040</v>
       </c>
@@ -18775,7 +18859,7 @@
       </c>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19">
       <c r="A28" s="10">
         <v>45048</v>
       </c>
@@ -18832,7 +18916,7 @@
       </c>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19">
       <c r="A29" s="10">
         <v>45054</v>
       </c>
@@ -18889,7 +18973,7 @@
       </c>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19">
       <c r="A30" s="10">
         <v>45061</v>
       </c>
@@ -18946,7 +19030,7 @@
       </c>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19">
       <c r="A31" s="10">
         <v>45068</v>
       </c>
@@ -19003,7 +19087,7 @@
       </c>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19">
       <c r="A32" s="10">
         <v>45076</v>
       </c>
@@ -19060,7 +19144,7 @@
       </c>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19">
       <c r="A33" s="10">
         <v>45082</v>
       </c>
@@ -19117,7 +19201,7 @@
       </c>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19">
       <c r="A34" s="10">
         <v>45089</v>
       </c>
@@ -19174,7 +19258,7 @@
       </c>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19">
       <c r="A35" s="10">
         <v>45096</v>
       </c>
@@ -19231,7 +19315,7 @@
       </c>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19">
       <c r="A36" s="10">
         <v>45103</v>
       </c>
@@ -19288,7 +19372,7 @@
       </c>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19">
       <c r="A37" s="10">
         <v>45110</v>
       </c>
@@ -19345,7 +19429,7 @@
       </c>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19">
       <c r="A38" s="10">
         <v>45117</v>
       </c>
@@ -19402,7 +19486,7 @@
       </c>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19">
       <c r="A39" s="10">
         <v>45124</v>
       </c>
@@ -19459,7 +19543,7 @@
       </c>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19">
       <c r="A40" s="10">
         <v>45131</v>
       </c>
@@ -19516,7 +19600,7 @@
       </c>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19">
       <c r="A41" s="10">
         <v>45138</v>
       </c>
@@ -19573,7 +19657,7 @@
       </c>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19">
       <c r="A42" s="10">
         <v>45145</v>
       </c>
@@ -19630,7 +19714,7 @@
       </c>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19">
       <c r="A43" s="10">
         <v>45152</v>
       </c>
@@ -19687,7 +19771,7 @@
       </c>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19">
       <c r="A44" s="10">
         <v>45159</v>
       </c>
@@ -19744,7 +19828,7 @@
       </c>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19">
       <c r="A45" s="10">
         <v>45166</v>
       </c>
@@ -19801,7 +19885,7 @@
       </c>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19">
       <c r="A46" s="10">
         <v>45173</v>
       </c>
@@ -19858,7 +19942,7 @@
       </c>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19">
       <c r="A47" s="10">
         <v>45180</v>
       </c>
@@ -19915,7 +19999,7 @@
       </c>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19">
       <c r="A48" s="10">
         <v>45187</v>
       </c>
@@ -19972,7 +20056,7 @@
       </c>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19">
       <c r="A49" s="10">
         <v>45194</v>
       </c>
@@ -20029,7 +20113,7 @@
       </c>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19">
       <c r="A50" s="10">
         <v>45209</v>
       </c>
@@ -20086,7 +20170,7 @@
       </c>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19">
       <c r="A51" s="10">
         <v>45215</v>
       </c>
@@ -20143,7 +20227,7 @@
       </c>
       <c r="S51" s="1"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19">
       <c r="A52" s="10">
         <v>45222</v>
       </c>
@@ -20200,7 +20284,7 @@
       </c>
       <c r="S52" s="1"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19">
       <c r="A53" s="10">
         <v>45229</v>
       </c>
@@ -20257,7 +20341,7 @@
       </c>
       <c r="S53" s="1"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19">
       <c r="A54" s="10">
         <v>45236</v>
       </c>
@@ -20314,7 +20398,7 @@
       </c>
       <c r="S54" s="1"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19">
       <c r="A55" s="10">
         <v>45243</v>
       </c>
@@ -20371,7 +20455,7 @@
       </c>
       <c r="S55" s="1"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19">
       <c r="A56" s="10">
         <v>45250</v>
       </c>
@@ -20428,7 +20512,7 @@
       </c>
       <c r="S56" s="1"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19">
       <c r="A57" s="10">
         <v>45257</v>
       </c>
@@ -20485,7 +20569,7 @@
       </c>
       <c r="S57" s="1"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19">
       <c r="A58" s="10">
         <v>45264</v>
       </c>
@@ -20542,7 +20626,7 @@
       </c>
       <c r="S58" s="1"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19">
       <c r="A59" s="10">
         <v>45271</v>
       </c>
@@ -20599,7 +20683,7 @@
       </c>
       <c r="S59" s="1"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19">
       <c r="A60" s="10">
         <v>45278</v>
       </c>
@@ -20656,7 +20740,7 @@
       </c>
       <c r="S60" s="1"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19">
       <c r="A61" s="10">
         <v>45286</v>
       </c>
@@ -20713,7 +20797,7 @@
       </c>
       <c r="S61" s="1"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19">
       <c r="A62" s="10">
         <v>45293</v>
       </c>
@@ -20770,7 +20854,7 @@
       </c>
       <c r="S62" s="1"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19">
       <c r="A63" s="10">
         <v>45299</v>
       </c>
@@ -20827,7 +20911,7 @@
       </c>
       <c r="S63" s="1"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19">
       <c r="A64" s="10">
         <v>45306</v>
       </c>
@@ -20884,7 +20968,7 @@
       </c>
       <c r="S64" s="1"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19">
       <c r="A65" s="10">
         <v>45313</v>
       </c>
@@ -20941,7 +21025,7 @@
       </c>
       <c r="S65" s="1"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19">
       <c r="A66" s="10">
         <v>45320</v>
       </c>
@@ -20998,7 +21082,7 @@
       </c>
       <c r="S66" s="1"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19">
       <c r="A67" s="10">
         <v>45327</v>
       </c>
@@ -21055,7 +21139,7 @@
       </c>
       <c r="S67" s="1"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19">
       <c r="A68" s="10">
         <v>45335</v>
       </c>
@@ -21112,7 +21196,7 @@
       </c>
       <c r="S68" s="1"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19">
       <c r="A69" s="10">
         <v>45341</v>
       </c>
@@ -21169,7 +21253,7 @@
       </c>
       <c r="S69" s="1"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19">
       <c r="A70" s="10">
         <v>45348</v>
       </c>
@@ -21226,7 +21310,7 @@
       </c>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19">
       <c r="A71" s="10">
         <v>45355</v>
       </c>
@@ -21283,7 +21367,7 @@
       </c>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19">
       <c r="A72" s="10">
         <v>45362</v>
       </c>
@@ -21340,7 +21424,7 @@
       </c>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19">
       <c r="A73" s="10">
         <v>45369</v>
       </c>
@@ -21397,7 +21481,7 @@
       </c>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19">
       <c r="A74" s="10">
         <v>45376</v>
       </c>
@@ -21454,7 +21538,7 @@
       </c>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19">
       <c r="A75" s="10">
         <v>45383</v>
       </c>
@@ -21511,7 +21595,7 @@
       </c>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19">
       <c r="A76" s="10">
         <v>45390</v>
       </c>
@@ -21568,7 +21652,7 @@
       </c>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19">
       <c r="A77" s="10">
         <v>45397</v>
       </c>
@@ -21625,7 +21709,7 @@
       </c>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19">
       <c r="A78" s="10">
         <v>45404</v>
       </c>
@@ -21682,7 +21766,7 @@
       </c>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19">
       <c r="A79" s="10">
         <v>45411</v>
       </c>
@@ -21739,7 +21823,7 @@
       </c>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19">
       <c r="A80" s="10">
         <v>45419</v>
       </c>
@@ -21796,7 +21880,7 @@
       </c>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19">
       <c r="A81" s="10">
         <v>45425</v>
       </c>
@@ -21853,7 +21937,7 @@
       </c>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19">
       <c r="A82" s="10">
         <v>45432</v>
       </c>
@@ -21910,7 +21994,7 @@
       </c>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19">
       <c r="A83" s="10">
         <v>45439</v>
       </c>
@@ -21967,7 +22051,7 @@
       </c>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19">
       <c r="A84" s="10">
         <v>45446</v>
       </c>
@@ -22024,7 +22108,7 @@
       </c>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19">
       <c r="A85" s="10">
         <v>45453</v>
       </c>
@@ -22081,7 +22165,7 @@
       </c>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19">
       <c r="A86" s="10">
         <v>45460</v>
       </c>
@@ -22138,7 +22222,7 @@
       </c>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19">
       <c r="A87" s="10">
         <v>45467</v>
       </c>
@@ -22195,7 +22279,7 @@
       </c>
       <c r="S87" s="1"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19">
       <c r="A88" s="10">
         <v>45474</v>
       </c>
@@ -22252,7 +22336,7 @@
       </c>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19">
       <c r="A89" s="10">
         <v>45481</v>
       </c>
@@ -22309,7 +22393,7 @@
       </c>
       <c r="S89" s="1"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19">
       <c r="A90" s="10">
         <v>45488</v>
       </c>
@@ -22366,7 +22450,7 @@
       </c>
       <c r="S90" s="1"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19">
       <c r="A91" s="10">
         <v>45495</v>
       </c>
@@ -22423,7 +22507,7 @@
       </c>
       <c r="S91" s="1"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19">
       <c r="A92" s="10">
         <v>45502</v>
       </c>
@@ -22480,7 +22564,7 @@
       </c>
       <c r="S92" s="1"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19">
       <c r="A93" s="10">
         <v>45509</v>
       </c>
@@ -22537,7 +22621,7 @@
       </c>
       <c r="S93" s="1"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19">
       <c r="A94" s="10">
         <v>45516</v>
       </c>
@@ -22594,7 +22678,7 @@
       </c>
       <c r="S94" s="1"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19">
       <c r="A95" s="10">
         <v>45523</v>
       </c>
@@ -22651,7 +22735,7 @@
       </c>
       <c r="S95" s="1"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19">
       <c r="A96" s="10">
         <v>45530</v>
       </c>
@@ -22708,7 +22792,7 @@
       </c>
       <c r="S96" s="1"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19">
       <c r="A97" s="10">
         <v>45537</v>
       </c>
@@ -22765,7 +22849,7 @@
       </c>
       <c r="S97" s="1"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19">
       <c r="A98" s="10">
         <v>45544</v>
       </c>
@@ -22822,7 +22906,7 @@
       </c>
       <c r="S98" s="1"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19">
       <c r="A99" s="10">
         <v>45558</v>
       </c>
@@ -22879,7 +22963,7 @@
       </c>
       <c r="S99" s="1"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19">
       <c r="A100" s="10">
         <v>45565</v>
       </c>
@@ -22936,7 +23020,7 @@
       </c>
       <c r="S100" s="1"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19">
       <c r="A101" s="10">
         <v>45572</v>
       </c>
@@ -22993,7 +23077,7 @@
       </c>
       <c r="S101" s="1"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19">
       <c r="A102" s="10">
         <v>45579</v>
       </c>
@@ -23050,7 +23134,7 @@
       </c>
       <c r="S102" s="1"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19">
       <c r="A103" s="10">
         <v>45586</v>
       </c>
@@ -23107,7 +23191,7 @@
       </c>
       <c r="S103" s="1"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19">
       <c r="A104" s="10">
         <v>45593</v>
       </c>
@@ -23164,7 +23248,7 @@
       </c>
       <c r="S104" s="1"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19">
       <c r="A105" s="10">
         <v>45600</v>
       </c>
@@ -23221,7 +23305,7 @@
       </c>
       <c r="S105" s="1"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19">
       <c r="A106" s="10">
         <v>45607</v>
       </c>
@@ -23278,7 +23362,7 @@
       </c>
       <c r="S106" s="1"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19">
       <c r="A107" s="10">
         <v>45614</v>
       </c>
@@ -23335,7 +23419,7 @@
       </c>
       <c r="S107" s="1"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19">
       <c r="A108" s="10">
         <v>45621</v>
       </c>
@@ -23392,7 +23476,7 @@
       </c>
       <c r="S108" s="1"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19">
       <c r="A109" s="10">
         <v>45628</v>
       </c>
@@ -23449,7 +23533,7 @@
       </c>
       <c r="S109" s="1"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19">
       <c r="A110" s="10">
         <v>45635</v>
       </c>
@@ -23506,7 +23590,7 @@
       </c>
       <c r="S110" s="1"/>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19">
       <c r="A111" s="10">
         <v>45642</v>
       </c>
@@ -23563,7 +23647,7 @@
       </c>
       <c r="S111" s="1"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19">
       <c r="A112" s="10">
         <v>45649</v>
       </c>
@@ -23620,7 +23704,7 @@
       </c>
       <c r="S112" s="1"/>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19">
       <c r="A113" s="10">
         <v>45656</v>
       </c>
@@ -23677,7 +23761,7 @@
       </c>
       <c r="S113" s="1"/>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19">
       <c r="A114" s="10">
         <v>45663</v>
       </c>
@@ -23734,7 +23818,7 @@
       </c>
       <c r="S114" s="1"/>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19">
       <c r="A115" s="10">
         <v>45670</v>
       </c>
@@ -23791,7 +23875,7 @@
       </c>
       <c r="S115" s="1"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19">
       <c r="A116" s="10">
         <v>45677</v>
       </c>
@@ -23848,7 +23932,7 @@
       </c>
       <c r="S116" s="1"/>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19">
       <c r="A117" s="10">
         <v>45691</v>
       </c>
@@ -23905,7 +23989,7 @@
       </c>
       <c r="S117" s="1"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19">
       <c r="A118" s="10">
         <v>45698</v>
       </c>
@@ -23962,7 +24046,7 @@
       </c>
       <c r="S118" s="1"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19">
       <c r="A119" s="10">
         <v>45705</v>
       </c>
@@ -24019,7 +24103,7 @@
       </c>
       <c r="S119" s="1"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19">
       <c r="A120" s="10">
         <v>45712</v>
       </c>
@@ -24076,7 +24160,7 @@
       </c>
       <c r="S120" s="1"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19">
       <c r="A121" s="10">
         <v>45720</v>
       </c>
@@ -24133,7 +24217,7 @@
       </c>
       <c r="S121" s="1"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19">
       <c r="A122" s="10">
         <v>45726</v>
       </c>
@@ -24190,7 +24274,7 @@
       </c>
       <c r="S122" s="1"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19">
       <c r="A123" s="10">
         <v>45733</v>
       </c>
@@ -24247,7 +24331,7 @@
       </c>
       <c r="S123" s="1"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19">
       <c r="A124" s="10">
         <v>45740</v>
       </c>
@@ -24304,7 +24388,7 @@
       </c>
       <c r="S124" s="1"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19">
       <c r="A125" s="10">
         <v>45747</v>
       </c>
@@ -24361,7 +24445,7 @@
       </c>
       <c r="S125" s="1"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19">
       <c r="A126" s="10">
         <v>45754</v>
       </c>
@@ -24418,7 +24502,7 @@
       </c>
       <c r="S126" s="1"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19">
       <c r="A127" s="10">
         <v>45761</v>
       </c>
@@ -24475,7 +24559,7 @@
       </c>
       <c r="S127" s="1"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19">
       <c r="A128" s="10">
         <v>45768</v>
       </c>
@@ -24532,7 +24616,7 @@
       </c>
       <c r="S128" s="1"/>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19">
       <c r="A129" s="10">
         <v>45775</v>
       </c>
@@ -24589,7 +24673,7 @@
       </c>
       <c r="S129" s="1"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19">
       <c r="A130" s="10">
         <v>45789</v>
       </c>
@@ -24646,7 +24730,7 @@
       </c>
       <c r="S130" s="1"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19">
       <c r="A131" s="10">
         <v>45796</v>
       </c>
@@ -24703,7 +24787,7 @@
       </c>
       <c r="S131" s="1"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19">
       <c r="A132" s="10">
         <v>45803</v>
       </c>
@@ -24760,7 +24844,7 @@
       </c>
       <c r="S132" s="1"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19">
       <c r="A133" s="10">
         <v>45810</v>
       </c>
@@ -24817,7 +24901,7 @@
       </c>
       <c r="S133" s="1"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19">
       <c r="A134" s="10">
         <v>45817</v>
       </c>
@@ -24874,7 +24958,7 @@
       </c>
       <c r="S134" s="1"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19">
       <c r="A135" s="10">
         <v>45824</v>
       </c>
@@ -24931,7 +25015,7 @@
       </c>
       <c r="S135" s="1"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19">
       <c r="A136" s="10">
         <v>45831</v>
       </c>
@@ -24988,7 +25072,7 @@
       </c>
       <c r="S136" s="1"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19">
       <c r="A137" s="10">
         <v>45838</v>
       </c>
@@ -25045,7 +25129,7 @@
       </c>
       <c r="S137" s="1"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19">
       <c r="A138" s="10">
         <v>45845</v>
       </c>
@@ -25102,7 +25186,7 @@
       </c>
       <c r="S138" s="1"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19">
       <c r="A139" s="10">
         <v>45852</v>
       </c>
@@ -25159,7 +25243,7 @@
       </c>
       <c r="S139" s="1"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19">
       <c r="A140" s="10">
         <v>45859</v>
       </c>
@@ -25216,7 +25300,7 @@
       </c>
       <c r="S140" s="1"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19">
       <c r="A141" s="10">
         <v>45866</v>
       </c>
@@ -25273,7 +25357,7 @@
       </c>
       <c r="S141" s="1"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19">
       <c r="A142" s="10">
         <v>45873</v>
       </c>
@@ -25330,7 +25414,7 @@
       </c>
       <c r="S142" s="1"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19">
       <c r="A143" s="10">
         <v>45880</v>
       </c>
@@ -25387,7 +25471,7 @@
       </c>
       <c r="S143" s="1"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19">
       <c r="A144" s="10">
         <v>45887</v>
       </c>
@@ -25444,7 +25528,7 @@
       </c>
       <c r="S144" s="1"/>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:19">
       <c r="A145" s="10">
         <v>45894</v>
       </c>
@@ -25501,7 +25585,7 @@
       </c>
       <c r="S145" s="1"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:19">
       <c r="A146" s="10">
         <v>45901</v>
       </c>
@@ -25558,7 +25642,7 @@
       </c>
       <c r="S146" s="1"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:19">
       <c r="A147" s="10">
         <v>45908</v>
       </c>
@@ -25615,7 +25699,7 @@
       </c>
       <c r="S147" s="1"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:19">
       <c r="A148" s="10">
         <v>45915</v>
       </c>
@@ -25672,7 +25756,7 @@
       </c>
       <c r="S148" s="1"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:19">
       <c r="A149" s="10">
         <v>45922</v>
       </c>
@@ -25729,7 +25813,7 @@
       </c>
       <c r="S149" s="1"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:19">
       <c r="A150" s="10">
         <v>45929</v>
       </c>
@@ -25786,7 +25870,7 @@
       </c>
       <c r="S150" s="1"/>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:19">
       <c r="A151" s="10">
         <v>45950</v>
       </c>
@@ -25843,7 +25927,7 @@
       </c>
       <c r="S151" s="1"/>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:19">
       <c r="A152" s="10">
         <v>45957</v>
       </c>
@@ -25900,7 +25984,7 @@
       </c>
       <c r="S152" s="1"/>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:19">
       <c r="A153" s="10">
         <v>45964</v>
       </c>
@@ -25957,7 +26041,7 @@
       </c>
       <c r="S153" s="1"/>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:19">
       <c r="A154" s="10">
         <v>45971</v>
       </c>
@@ -26014,7 +26098,7 @@
       </c>
       <c r="S154" s="1"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:19">
       <c r="A155" s="10">
         <v>45978</v>
       </c>
@@ -26071,7 +26155,7 @@
       </c>
       <c r="S155" s="1"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:19">
       <c r="A156" s="10">
         <v>45985</v>
       </c>
@@ -26128,7 +26212,7 @@
       </c>
       <c r="S156" s="1"/>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:19">
       <c r="A157" s="10">
         <v>45992</v>
       </c>
@@ -26185,7 +26269,7 @@
       </c>
       <c r="S157" s="1"/>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:19">
       <c r="A158" s="10">
         <v>45999</v>
       </c>
@@ -26242,7 +26326,7 @@
       </c>
       <c r="S158" s="1"/>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:19">
       <c r="A159" s="10">
         <v>46006</v>
       </c>
@@ -26299,7 +26383,7 @@
       </c>
       <c r="S159" s="1"/>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:19">
       <c r="A160" s="10">
         <v>46013</v>
       </c>
@@ -26356,7 +26440,7 @@
       </c>
       <c r="S160" s="1"/>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:19">
       <c r="A161" s="10">
         <v>46020</v>
       </c>
@@ -26413,7 +26497,7 @@
       </c>
       <c r="S161" s="1"/>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:19">
       <c r="A162" s="10">
         <v>46034</v>
       </c>
@@ -26470,7 +26554,7 @@
       </c>
       <c r="S162" s="1"/>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:19">
       <c r="A163" s="10">
         <v>46041</v>
       </c>
@@ -26527,7 +26611,7 @@
       </c>
       <c r="S163" s="1"/>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:19">
       <c r="A164" s="10">
         <v>46048</v>
       </c>
@@ -26584,7 +26668,7 @@
       </c>
       <c r="S164" s="1"/>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:19">
       <c r="A165" s="10">
         <v>46055</v>
       </c>
@@ -26641,7 +26725,7 @@
       </c>
       <c r="S165" s="1"/>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:19">
       <c r="A166" s="10">
         <v>46062</v>
       </c>
@@ -26698,7 +26782,7 @@
       </c>
       <c r="S166" s="1"/>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:19">
       <c r="A167" s="10">
         <v>46076</v>
       </c>
@@ -26754,7 +26838,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:19">
       <c r="A168" s="10">
         <v>46084</v>
       </c>
@@ -26810,7 +26894,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:19">
       <c r="A169" s="10">
         <v>46090</v>
       </c>
@@ -26866,7 +26950,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:19">
       <c r="A170" s="10">
         <v>46097</v>
       </c>
@@ -26922,7 +27006,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:19">
       <c r="A171" s="10">
         <v>46104</v>
       </c>
@@ -26978,7 +27062,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:19">
       <c r="A172" s="10">
         <v>46111</v>
       </c>
@@ -27034,7 +27118,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:19">
       <c r="A173" s="10">
         <v>46118</v>
       </c>
@@ -27090,7 +27174,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:19">
       <c r="A174" s="10">
         <v>46125</v>
       </c>
@@ -27146,7 +27230,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:19">
       <c r="A175" s="10">
         <v>46132</v>
       </c>
@@ -27202,7 +27286,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:19">
       <c r="A176" s="10">
         <v>46139</v>
       </c>
@@ -27258,7 +27342,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18">
       <c r="A177" s="10">
         <v>46153</v>
       </c>
@@ -27314,7 +27398,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18">
       <c r="A178" s="10">
         <v>46160</v>
       </c>
@@ -27370,7 +27454,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18">
       <c r="A179" s="10">
         <v>46168</v>
       </c>
@@ -27426,7 +27510,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18">
       <c r="A180" s="10">
         <v>46174</v>
       </c>
@@ -27480,6 +27564,62 @@
       </c>
       <c r="R180" s="7">
         <v>1142</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18">
+      <c r="A181" s="10">
+        <v>46181</v>
+      </c>
+      <c r="B181" s="10">
+        <v>46181</v>
+      </c>
+      <c r="C181" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E181" s="7">
+        <v>3042</v>
+      </c>
+      <c r="F181" s="7">
+        <v>4247</v>
+      </c>
+      <c r="G181" s="7">
+        <v>5393</v>
+      </c>
+      <c r="H181" s="7">
+        <v>3679</v>
+      </c>
+      <c r="I181" s="7">
+        <v>4877</v>
+      </c>
+      <c r="J181" s="7">
+        <v>6011</v>
+      </c>
+      <c r="K181" s="7">
+        <v>2423</v>
+      </c>
+      <c r="L181" s="7">
+        <v>5396</v>
+      </c>
+      <c r="M181" s="7">
+        <v>4321</v>
+      </c>
+      <c r="N181" s="7">
+        <v>3274</v>
+      </c>
+      <c r="O181" s="7">
+        <v>4679</v>
+      </c>
+      <c r="P181" s="7">
+        <v>51</v>
+      </c>
+      <c r="Q181" s="7">
+        <v>227</v>
+      </c>
+      <c r="R181" s="7">
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -27501,14 +27641,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EF7E42-3273-4C27-80E3-741AD2FB330F}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.21875" style="2"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="2" max="2" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3" ht="16">
       <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
@@ -27516,7 +27656,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
         <v>34</v>
       </c>
@@ -27537,9 +27677,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BD5038-94A8-4C07-9E87-4FDF24EEDBD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="9.21875" style="2"/>
+    <col min="1" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
